--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -357,8 +357,305 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁초댕기.csv</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁초댕기</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H3" s="2">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>89</v>
+      </c>
+      <c r="K3" s="2">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/궁초댕기.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이 피었네.csv</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이 피었네</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C / Eb</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H4" s="2">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>56</v>
+      </c>
+      <c r="K4" s="2">
+        <v>6</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/꽃이 피었네.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남원산성.csv</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남원산성</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>95</v>
+      </c>
+      <c r="K5" s="2">
+        <v>6</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/남원산성.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농부가.csv</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농부가</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="H6" s="2">
+        <v>12</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>84</v>
+      </c>
+      <c r="K6" s="2">
+        <v>9</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/농부가.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님타령.csv</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님타령</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H7" s="2">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>152</v>
+      </c>
+      <c r="K7" s="2">
+        <v>13</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/님타령.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O2"/>
+  <autoFilter ref="A1:O7"/>
 </worksheet>
 </file>
 
@@ -509,8 +806,288 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/궁초댕기.png</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_궁초댕기.tsv</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁초댕기</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F3" s="2">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2">
+        <v>89</v>
+      </c>
+      <c r="J3" s="2">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">궁초댕기.csv</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백에 "정악청이" 표기. 양식은 정간 번호 2개(1·2, 3·4…)가 한 칸 → 위쪽 절반=홀수, 아래쪽 절반=짝수 정간으로 나눔. 8줄 사용(8줄은 점·연음만). AI 재판독 초안.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/꽃이 피었네.png</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_꽃이 피었네.tsv</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이 피었네</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F4" s="2">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>56</v>
+      </c>
+      <c r="J4" s="2">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃이 피었네.csv</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백 "C key / Eb key". 인쇄 1줄은 비어 있고 2~5줄 사용(원본 번호 그대로). 번호 2개가 한 칸 → 위=홀수, 아래=짝수 정간(세 개 쌓이면 위 둘=홀수). AI 재판독 초안.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/남원산성.png</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_남원산성.tsv</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남원산성</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F5" s="2">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2">
+        <v>6</v>
+      </c>
+      <c r="I5" s="2">
+        <v>95</v>
+      </c>
+      <c r="J5" s="2">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남원산성.csv</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백 "C key" 표기. 6줄 사용(7·8줄 빈칸). 하단 메모: "※ 높으면 潢을…, 潢에서 無까지"(음역 설명). 율명 오른쪽 )) 곡선 표시(요성으로 보임)는 기호표에 없어 생략. 2줄 가사 칸의 세로선·∨ 표시는 생략. 번호 2개가 한 칸 → 위=홀수, 아래=짝수 정간. AI 재판독 초안.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/농부가.png</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_농부가.tsv</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농부가</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F6" s="2">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2">
+        <v>7</v>
+      </c>
+      <c r="I6" s="2">
+        <v>84</v>
+      </c>
+      <c r="J6" s="2">
+        <v>9</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농부가.csv</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백 "남도민요 &lt;중모리&gt;". 12정간, 굵은 선 3칸마다. 7줄 사용(8줄 빈칸). 율명 옆 물결선(요성)은 기호표에 없어 생략. 하단 메모 "※ 전체적으로 노래의 요성에 따라(요성함)". 일부 율명 오른쪽 작은 검은 세모(▼) 표시 생략. AI 재판독 초안.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/님타령.png</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_님타령.tsv</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님타령</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F7" s="2">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10</v>
+      </c>
+      <c r="I7" s="2">
+        <v>152</v>
+      </c>
+      <c r="J7" s="2">
+        <v>13</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님타령.csv</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양식이 180° 뒤집혀 인쇄됨(쪽 번호·줄 번호가 거꾸로). 손글씨 기준으로 오른쪽부터 1줄. 번호 2개가 한 칸 → 위=홀수, 아래=짝수 정간(세 개 쌓이면 위 둘=홀수). 6줄 9~16정간은 "(간주)": 율명 없이 장구 구음(덩 기덕 덩 다라라 쿵 기덕 쿵 따)만 적혀 비고에 기록. 9줄은 16정간 아래 여백까지 이어 씀(南 ⁚ ⁚ △, 비고 참조). 10줄은 왼쪽 여백의 &lt;전주&gt;(곡 앞에 연주)로 칸 구분이 양식과 달라 정간 위치는 추정, 아래 여백에 X로 지운 칸과 연음이 더 있음. 물결선(요성) 생략. AI 재판독 초안.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N7"/>
 </worksheet>
 </file>
 
@@ -569,8 +1146,44 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님타령.csv</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/님타령.png</t>
+        </is>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가로줄로 지운 글자(杏/林 모양)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
 </worksheet>
 </file>
 
@@ -605,6 +1218,26 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U+003F</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 확인</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -5758,7 +5758,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 16정간 격자, 굵은 선 4칸마다 → 4/4·16. 상단 제목 칸 "꼭두각시(자진머리) (2번)". 율명 열 10개 중 맨 오른쪽 열(1줄)과 가운데 열(6줄)은 비어 있어 내용은 2~5줄, 7~10줄. 가사 칸은 모두 비어 있음. 율명 옆 작은 ▼ 표시와 ∴ 점, 율명 몇 개에 친 동그라미(潢), 체크 표시, 상단 ② 와 화살표 곡선은 기호표에 없어 생략. 같은 가락(姑―仲/南^/潢無南/仲姑△ 등) 반복은 같은 글자로 통일. AI 재판독 초안.</t>
+          <t xml:space="preserve">손으로 그린 16정간 격자, 굵은 선 4칸마다 → 4/4·16. 상단 제목 칸 "꼭두각시(자진머리) (2번)". 율명 열 10개 중 맨 오른쪽 열(1줄)과 가운데 열(6줄)은 비어 있어 내용은 2~5줄, 7~10줄. 가사 칸은 모두 비어 있음. 율명 옆 작은 ▼ 표시와 ∴ 점, 율명 몇 개에 친 동그라미(潢), 체크 표시, 상단 ② 와 화살표 곡선은 기호표에 없어 생략. 같은 가락(姑–仲/南^/潢無南/仲姑△ 등) 반복은 같은 글자로 통일. AI 재판독 초안.</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄된 12정간 양식(굵은 선 3칸마다 → 3/4, 용지 번호 "- 197 -"). 위 줄 번호 오른쪽부터 1, 왼쪽에 정간 1~12. 오른쪽 여백에 제목 "석별가"와 장단 "굿거리"를 세로로 적어 둠. 내용 있는 줄은 오른쪽 6줄(7~8줄은 빔). 각 율명 줄 오른쪽 좁은 칸에 손글씨 가사가 있어 그대로 전사함(5번째 줄 후렴 "가세 가세 나도 가세"가 가장 또렷함). 청황 潢·청태 汰·청림 淋·중성 南/姑가 지배적. 정간8~9에 율명이 2~3자 쌓여 있고 정간12는 종지 꾸밈(―/○)으로 보임. 흘림체가 심해 일부 가사·율명은 비고에 불확실 표시. AI 재판독.</t>
+          <t xml:space="preserve">인쇄된 12정간 양식(굵은 선 3칸마다 → 3/4, 용지 번호 "- 197 -"). 위 줄 번호 오른쪽부터 1, 왼쪽에 정간 1~12. 오른쪽 여백에 제목 "석별가"와 장단 "굿거리"를 세로로 적어 둠. 내용 있는 줄은 오른쪽 6줄(7~8줄은 빔). 각 율명 줄 오른쪽 좁은 칸에 손글씨 가사가 있어 그대로 전사함(5번째 줄 후렴 "가세 가세 나도 가세"가 가장 또렷함). 청황 潢·청태 汰·청림 淋·중성 南/姑가 지배적. 정간8~9에 율명이 2~3자 쌓여 있고 정간12는 종지 꾸밈(–/○)으로 보임. 흘림체가 심해 일부 가사·율명은 비고에 불확실 표시. AI 재판독.</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목 없는 손채보 조각. 손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12. 거의 빈 용지로, 오른쪽에서 두 줄에만 내용이 있음(그 오른쪽 끝 열은 비어 있어 율명 줄 1부터 셈). 줄2는 율명 없이 짧은 사선(ﾉ)·세로 획(―)과 세모만 있음(기호표 밖 획은 ﾉ·―로 적음). 가사: 깐다 깐다 정든 님이 떠나간다.</t>
+          <t xml:space="preserve">제목 없는 손채보 조각. 손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12. 거의 빈 용지로, 오른쪽에서 두 줄에만 내용이 있음(그 오른쪽 끝 열은 비어 있어 율명 줄 1부터 셈). 줄2는 율명 없이 짧은 사선(ﾉ)·세로 획(–)과 세모만 있음(기호표 밖 획은 ﾉ·–로 적음). 가사: 깐다 깐다 정든 님이 떠나간다.</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -15,24 +15,24 @@
   <fonts count="4">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -158,7 +158,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -186,7 +185,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -5056,8 +5056,53 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄철나비.csv</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄철나비</t>
+        </is>
+      </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H88" s="2">
+        <v>16</v>
+      </c>
+      <c r="I88" s="2">
+        <v>1</v>
+      </c>
+      <c r="J88" s="2">
+        <v>47</v>
+      </c>
+      <c r="K88" s="2">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검수 xlsx 직접 입력 (거스러미 돈돈날이.xlsx 복사)</t>
+        </is>
+      </c>
+      <c r="O88" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O87"/>
+  <autoFilter ref="A1:O88"/>
 </worksheet>
 </file>
 

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -951,6 +951,70 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">꽃 타령 (자진모리)-2.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">꽃 타령-2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">비고 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="궁서체"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">민요채보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="궁서체"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">꽃 타령</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="궁서체"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.png</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -976,7 +1040,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">꽃은 모리</t>
+      <t xml:space="preserve">자진모리</t>
     </r>
     <r>
       <rPr>
@@ -990,105 +1054,6 @@
   </si>
   <si>
     <t xml:space="preserve">꽃 타령</t>
-  </si>
-  <si>
-    <t xml:space="preserve">꽃은 모리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">비고 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">민요채보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 타령</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.png</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">꽃 타령 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">자진모리</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">).csv</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">C#</t>
@@ -50846,7 +50811,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -50860,7 +50825,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>31</v>
@@ -50872,10 +50837,10 @@
         <v>28</v>
       </c>
       <c r="N13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50883,10 +50848,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>43</v>
@@ -54665,7 +54630,7 @@
     </row>
     <row r="13" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>360</v>
@@ -54674,7 +54639,7 @@
         <v>67</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>17</v>
@@ -54713,7 +54678,7 @@
         <v>362</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>43</v>
@@ -54741,7 +54706,7 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14" s="8" t="s">
         <v>363</v>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -1367,42 +1367,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">노래가락 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">채보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3) </t>
-    </r>
     <r>
       <rPr>
         <sz val="11"/>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -1457,42 +1457,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">노래가락 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="나눔고딕"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">채보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3) </t>
-    </r>
     <r>
       <rPr>
         <sz val="11"/>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -50967,21 +50967,21 @@
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>10</v>
+      <c r="J18" s="6">
+        <v>93</v>
+      </c>
+      <c r="K18" s="6">
+        <v>4</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N18" s="5"/>
       <c r="O18" s="5" t="s">
         <v>88</v>
       </c>
@@ -54789,11 +54789,11 @@
       <c r="H18" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>10</v>
+      <c r="I18" s="6">
+        <v>93</v>
+      </c>
+      <c r="J18" s="6">
+        <v>4</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
@@ -54802,8 +54802,10 @@
       <c r="M18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N18" s="8" t="s">
-        <v>371</v>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12정간·굵은 선 3칸마다(인쇄 정간 번호 1~12, 줄 번호 오른쪽 1~8). 손채보, 가사는 각 율명 줄 오른쪽 칸. 10-13 전면 재판독(이전 TSV 는 이미지와 다른 내용). 줄5 번호 위 v 표시는 생략.</t>
+        </is>
       </c>
     </row>
     <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -51185,17 +51185,19 @@
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-      <c r="G23" s="4" t="s">
-        <v>27</v>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>4</v>
@@ -51203,10 +51205,16 @@
       <c r="L23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="5"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 25%, 박자 근사</t>
+        </is>
+      </c>
       <c r="O23" s="5" t="s">
         <v>105</v>
       </c>
@@ -51230,25 +51238,29 @@
         <v>17</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M24" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>35</v>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1, 박자 근사</t>
+        </is>
       </c>
       <c r="O24" s="5" t="s">
         <v>108</v>
@@ -55074,11 +55086,13 @@
       <c r="D23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>27</v>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>2</v>
@@ -55087,7 +55101,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>4</v>
@@ -55099,8 +55113,10 @@
       <c r="M23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N23" s="5" t="s">
-        <v>381</v>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백에 세로로 손글씨 "능계가락 신방곡". 16정간 인쇄 양식이지만 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 오른쪽부터 줄1, 줄2. 줄3 이하(왼쪽 열들)는 빈 격자. 하단 양식 번호 "- 196 -"(16정간 용지). 율명 옆 좁은 가사 칸은 비어 있어 가사는 비움. 한 높이에 나란히 쓴 두 율명은 왼쪽→오른쪽 순으로 적음. 古 모양: 女변 있으면 姑, 없으면 南.</t>
+        </is>
       </c>
     </row>
     <row r="24" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55120,7 +55136,7 @@
         <v>17</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>10</v>
@@ -55129,10 +55145,10 @@
         <v>10</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>1</v>
@@ -55141,8 +55157,10 @@
       <c r="M24" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N24" s="5" t="s">
-        <v>383</v>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양식이 180° 뒤집혀 인쇄됨(쪽 번호·줄 번호가 거꾸로). 손글씨 기준으로 오른쪽부터 1줄. 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 6줄 5~8정간은 "(간주)": 율명 없이 장구 구음(덩 기덕 덩 다라라 쿵 기덕 쿵 따)만 적혀 비고에 기록. 9줄은 8정간 아래 여백까지 이어 씀(南 ⁚ ⁚ △, 비고 참조). 10줄은 왼쪽 여백의 &lt;전주&gt;(곡 앞에 연주)로 칸 구분이 양식과 달라 정간 위치는 추정, 아래 여백에 X로 지운 칸과 연음이 더 있음. 물결선(요성) 생략. AI 재판독 초안.</t>
+        </is>
       </c>
     </row>
     <row r="25" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -14,8 +14,8 @@
     <sheet name="글자 빈도" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$91</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$88</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$94</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$91</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'확인 필요 글자'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -50202,7 +50202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.74"/>
@@ -51339,17 +51339,17 @@
         <v>84</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N26" s="5"/>
       <c r="O26" s="5" t="s">
         <v>118</v>
       </c>
@@ -51382,13 +51382,15 @@
         <v>120</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="6" t="s">
-        <v>18</v>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5" t="s">
@@ -51402,25 +51404,31 @@
       <c r="B28" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>49</v>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매화 타령</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
-      <c r="G28" s="4" t="s">
-        <v>17</v>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>9</v>
@@ -51428,10 +51436,16 @@
       <c r="L28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N28" s="5"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
+      </c>
       <c r="O28" s="5" t="s">
         <v>124</v>
       </c>
@@ -51443,16 +51457,22 @@
       <c r="B29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>49</v>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽금포 타령</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
-      <c r="G29" s="4" t="s">
-        <v>34</v>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H29" s="6" t="n">
         <v>12</v>
@@ -51461,19 +51481,23 @@
         <v>1</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>127</v>
+        <v>1</v>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
+        </is>
       </c>
       <c r="O29" s="5" t="s">
         <v>128</v>
@@ -51486,16 +51510,22 @@
       <c r="B30" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>39</v>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물레타령</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
-      <c r="G30" s="4" t="s">
-        <v>34</v>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H30" s="6" t="n">
         <v>12</v>
@@ -51504,19 +51534,23 @@
         <v>1</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>131</v>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 22%</t>
+        </is>
       </c>
       <c r="O30" s="5" t="s">
         <v>132</v>
@@ -51529,16 +51563,22 @@
       <c r="B31" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>116</v>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밀양 아리랑</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="4" t="s">
-        <v>34</v>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H31" s="6" t="n">
         <v>12</v>
@@ -51547,22 +51587,28 @@
         <v>1</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N31" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="O31" s="5" t="s">
-        <v>136</v>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
+        </is>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51572,19 +51618,25 @@
       <c r="B32" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>49</v>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
-      <c r="G32" s="4" t="s">
-        <v>17</v>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
@@ -51598,10 +51650,16 @@
       <c r="L32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N32" s="5"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
       <c r="O32" s="5" t="s">
         <v>139</v>
       </c>
@@ -51613,36 +51671,48 @@
       <c r="B33" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>141</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느리게</t>
+        </is>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
-      <c r="G33" s="4" t="s">
-        <v>17</v>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="5"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="s">
         <v>142</v>
       </c>
@@ -51654,16 +51724,22 @@
       <c r="B34" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>49</v>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃노래</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
-      <c r="G34" s="4" t="s">
-        <v>34</v>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H34" s="6" t="n">
         <v>12</v>
@@ -51672,16 +51748,18 @@
         <v>1</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="6" t="s">
-        <v>18</v>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5" t="s">
@@ -51695,16 +51773,22 @@
       <c r="B35" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>49</v>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베틀가</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
-      <c r="G35" s="4" t="s">
-        <v>34</v>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H35" s="6" t="n">
         <v>12</v>
@@ -51716,16 +51800,20 @@
         <v>48</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" s="5" t="s">
-        <v>148</v>
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
       </c>
       <c r="O35" s="5" t="s">
         <v>149</v>
@@ -51738,16 +51826,22 @@
       <c r="B36" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>39</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">북간도 아리랑</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
-      <c r="G36" s="4" t="s">
-        <v>34</v>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H36" s="6" t="n">
         <v>12</v>
@@ -51756,16 +51850,18 @@
         <v>1</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="6" t="s">
-        <v>18</v>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
@@ -51779,32 +51875,38 @@
       <c r="B37" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>154</v>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가</t>
+        </is>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
-      <c r="G37" s="4" t="s">
-        <v>27</v>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M37" s="6" t="s">
-        <v>18</v>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5" t="s">
@@ -51818,37 +51920,47 @@
       <c r="B38" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>49</v>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사철가</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
-      <c r="G38" s="4" t="s">
-        <v>34</v>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>158</v>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 15%</t>
+        </is>
       </c>
       <c r="O38" s="5" t="s">
         <v>159</v>
@@ -51861,36 +51973,48 @@
       <c r="B39" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>49</v>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사철가</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="4" t="s">
-        <v>27</v>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N39" s="5"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 18%</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="s">
         <v>161</v>
       </c>
@@ -51902,36 +52026,48 @@
       <c r="B40" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>49</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상사 천리몽</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
-      <c r="G40" s="4" t="s">
-        <v>27</v>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N40" s="5"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 25%, 박자 근사</t>
+        </is>
+      </c>
       <c r="O40" s="5" t="s">
         <v>164</v>
       </c>
@@ -51943,14 +52079,18 @@
       <c r="B41" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>166</v>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상주 모심기</t>
+        </is>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
-      <c r="G41" s="4" t="s">
-        <v>34</v>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H41" s="6" t="n">
         <v>12</v>
@@ -51967,11 +52107,15 @@
       <c r="L41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>167</v>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 21%</t>
+        </is>
       </c>
       <c r="O41" s="5" t="s">
         <v>168</v>
@@ -51984,18 +52128,26 @@
       <c r="B42" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>72</v>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F42" s="6"/>
-      <c r="G42" s="4" t="s">
-        <v>34</v>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H42" s="6" t="n">
         <v>12</v>
@@ -52004,20 +52156,20 @@
         <v>1</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>171</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N42" s="5"/>
       <c r="O42" s="5" t="s">
         <v>172</v>
       </c>
@@ -52029,18 +52181,26 @@
       <c r="B43" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>72</v>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 타령-2</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2절</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F43" s="6"/>
-      <c r="G43" s="4" t="s">
-        <v>34</v>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H43" s="6" t="n">
         <v>12</v>
@@ -52052,13 +52212,15 @@
         <v>111</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M43" s="6" t="s">
-        <v>18</v>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5" t="s">
@@ -52072,18 +52234,22 @@
       <c r="B44" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>49</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">석별가</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E44" s="6"/>
-      <c r="F44" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>34</v>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H44" s="6" t="n">
         <v>12</v>
@@ -52092,16 +52258,18 @@
         <v>1</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="6" t="s">
-        <v>18</v>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5" t="s">
@@ -52115,34 +52283,42 @@
       <c r="B45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>49</v>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선화공주</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
-      <c r="G45" s="4" t="s">
-        <v>17</v>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="6" t="s">
-        <v>18</v>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5" t="s">
@@ -52156,34 +52332,42 @@
       <c r="B46" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>186</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신 만고강산</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남도민요</t>
+        </is>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
-      <c r="G46" s="4" t="s">
-        <v>17</v>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H46" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="6" t="s">
-        <v>18</v>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5" t="s">
@@ -52197,25 +52381,31 @@
       <c r="B47" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>49</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신 천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
-      <c r="G47" s="4" t="s">
-        <v>17</v>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>2</v>
@@ -52223,8 +52413,10 @@
       <c r="L47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="6" t="s">
-        <v>18</v>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5" t="s">
@@ -52238,38 +52430,44 @@
       <c r="B48" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>49</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신고산 타령</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
-      <c r="G48" s="4" t="s">
-        <v>17</v>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N48" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N48" s="5"/>
       <c r="O48" s="5" t="s">
         <v>193</v>
       </c>
@@ -52281,16 +52479,22 @@
       <c r="B49" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>196</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가 중모리</t>
+        </is>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
-      <c r="G49" s="4" t="s">
-        <v>34</v>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H49" s="6" t="n">
         <v>12</v>
@@ -52299,16 +52503,18 @@
         <v>1</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="6" t="s">
-        <v>18</v>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5" t="s">
@@ -52322,16 +52528,22 @@
       <c r="B50" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>39</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="4" t="s">
-        <v>34</v>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H50" s="6" t="n">
         <v>12</v>
@@ -52340,20 +52552,20 @@
         <v>1</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N50" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N50" s="5"/>
       <c r="O50" s="5" t="s">
         <v>199</v>
       </c>
@@ -52365,14 +52577,18 @@
       <c r="B51" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>201</v>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑 낭낭</t>
+        </is>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="4" t="s">
-        <v>17</v>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H51" s="6" t="n">
         <v>16</v>
@@ -52381,19 +52597,23 @@
         <v>1</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N51" s="5" t="s">
-        <v>202</v>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
       </c>
       <c r="O51" s="5" t="s">
         <v>203</v>
@@ -52406,16 +52626,22 @@
       <c r="B52" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>43</v>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑 목동</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자진모리</t>
+        </is>
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
-      <c r="G52" s="4" t="s">
-        <v>17</v>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H52" s="6" t="n">
         <v>16</v>
@@ -52427,16 +52653,20 @@
         <v>80</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N52" s="5" t="s">
-        <v>73</v>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
       </c>
       <c r="O52" s="5" t="s">
         <v>206</v>
@@ -52449,38 +52679,52 @@
       <c r="B53" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>209</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">애수의 가을밤</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정악key</t>
+        </is>
       </c>
       <c r="F53" s="6"/>
-      <c r="G53" s="4" t="s">
-        <v>17</v>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N53" s="5"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="s">
         <v>210</v>
       </c>
@@ -52492,18 +52736,26 @@
       <c r="B54" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>72</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야월삼경</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F54" s="6"/>
-      <c r="G54" s="4" t="s">
-        <v>34</v>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H54" s="6" t="n">
         <v>12</v>
@@ -52512,16 +52764,18 @@
         <v>1</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M54" s="6" t="s">
-        <v>18</v>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5" t="s">
@@ -52535,16 +52789,22 @@
       <c r="B55" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>49</v>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양류가</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
-      <c r="G55" s="4" t="s">
-        <v>34</v>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H55" s="6" t="n">
         <v>12</v>
@@ -52553,19 +52813,23 @@
         <v>1</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N55" s="5" t="s">
-        <v>216</v>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 20%</t>
+        </is>
       </c>
       <c r="O55" s="5" t="s">
         <v>217</v>
@@ -52578,42 +52842,56 @@
       <c r="B56" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>219</v>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양류가</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대금키</t>
+        </is>
       </c>
       <c r="F56" s="6"/>
-      <c r="G56" s="4" t="s">
-        <v>34</v>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H56" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M56" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N56" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="O56" s="5" t="s">
-        <v>221</v>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52623,18 +52901,26 @@
       <c r="B57" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>72</v>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양산도</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F57" s="6"/>
-      <c r="G57" s="4" t="s">
-        <v>34</v>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H57" s="6" t="n">
         <v>12</v>
@@ -52643,20 +52929,20 @@
         <v>1</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N57" s="5" t="s">
-        <v>131</v>
-      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N57" s="5"/>
       <c r="O57" s="5" t="s">
         <v>224</v>
       </c>
@@ -52668,37 +52954,47 @@
       <c r="B58" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>116</v>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">영천 아리랑</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
-      <c r="G58" s="4" t="s">
-        <v>34</v>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H58" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N58" s="5" t="s">
-        <v>216</v>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
       </c>
       <c r="O58" s="5" t="s">
         <v>227</v>
@@ -52711,40 +53007,52 @@
       <c r="B59" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>49</v>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오봉산 타령</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
-      <c r="G59" s="4" t="s">
-        <v>34</v>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N59" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O59" s="5" t="s">
-        <v>230</v>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52754,14 +53062,18 @@
       <c r="B60" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>232</v>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">옹이</t>
+        </is>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
-      <c r="G60" s="4" t="s">
-        <v>34</v>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H60" s="6" t="n">
         <v>12</v>
@@ -52770,20 +53082,20 @@
         <v>1</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M60" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N60" s="5" t="s">
-        <v>233</v>
-      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N60" s="5"/>
       <c r="O60" s="5" t="s">
         <v>234</v>
       </c>
@@ -52795,18 +53107,26 @@
       <c r="B61" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>72</v>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울산 아가씨</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F61" s="6"/>
-      <c r="G61" s="4" t="s">
-        <v>34</v>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H61" s="6" t="n">
         <v>12</v>
@@ -52815,18 +53135,24 @@
         <v>1</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N61" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="s">
         <v>237</v>
       </c>
@@ -52838,38 +53164,44 @@
       <c r="B62" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>240</v>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별가</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느릿 굿거리</t>
+        </is>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
-      <c r="G62" s="4" t="s">
-        <v>17</v>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M62" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N62" s="5" t="s">
-        <v>241</v>
-      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N62" s="5"/>
       <c r="O62" s="5" t="s">
         <v>242</v>
       </c>
@@ -52881,36 +53213,48 @@
       <c r="B63" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>245</v>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후렴</t>
+        </is>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
-      <c r="G63" s="4" t="s">
-        <v>34</v>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N63" s="5"/>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
+      </c>
       <c r="O63" s="5" t="s">
         <v>246</v>
       </c>
@@ -52922,16 +53266,22 @@
       <c r="B64" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>39</v>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전라도 산타령</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
-      <c r="G64" s="4" t="s">
-        <v>34</v>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H64" s="6" t="n">
         <v>12</v>
@@ -52943,17 +53293,17 @@
         <v>47</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M64" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N64" s="5" t="s">
-        <v>249</v>
-      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N64" s="5"/>
       <c r="O64" s="5" t="s">
         <v>250</v>
       </c>
@@ -52965,14 +53315,18 @@
       <c r="B65" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>252</v>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제목없음 (이미지 (28))</t>
+        </is>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
-      <c r="G65" s="4" t="s">
-        <v>34</v>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H65" s="6" t="n">
         <v>12</v>
@@ -52984,16 +53338,20 @@
         <v>17</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N65" s="5" t="s">
-        <v>253</v>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 53%, 제목 없음</t>
+        </is>
       </c>
       <c r="O65" s="5" t="s">
         <v>254</v>
@@ -53006,16 +53364,22 @@
       <c r="B66" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>257</v>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령 / 닐리리야</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리 / 굿거리</t>
+        </is>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
-      <c r="G66" s="4" t="s">
-        <v>34</v>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H66" s="6" t="n">
         <v>12</v>
@@ -53027,16 +53391,20 @@
         <v>84</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M66" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N66" s="5" t="s">
-        <v>54</v>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 18%, 한 장에 두 곡</t>
+        </is>
       </c>
       <c r="O66" s="5" t="s">
         <v>258</v>
@@ -53049,16 +53417,22 @@
       <c r="B67" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>257</v>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령 / 담바귀 타령</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리 / 굿거리</t>
+        </is>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
-      <c r="G67" s="4" t="s">
-        <v>34</v>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H67" s="6" t="n">
         <v>12</v>
@@ -53070,16 +53444,20 @@
         <v>95</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M67" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N67" s="5" t="s">
-        <v>54</v>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
       </c>
       <c r="O67" s="5" t="s">
         <v>261</v>
@@ -53092,16 +53470,22 @@
       <c r="B68" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>264</v>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멜로디버전</t>
+        </is>
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
-      <c r="G68" s="4" t="s">
-        <v>34</v>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H68" s="6" t="n">
         <v>12</v>
@@ -53113,16 +53497,20 @@
         <v>119</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N68" s="5" t="s">
-        <v>233</v>
+        <v>1</v>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
+        </is>
       </c>
       <c r="O68" s="5" t="s">
         <v>265</v>
@@ -53135,16 +53523,22 @@
       <c r="B69" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>49</v>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
-      <c r="G69" s="4" t="s">
-        <v>34</v>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H69" s="6" t="n">
         <v>12</v>
@@ -53156,13 +53550,15 @@
         <v>113</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M69" s="6" t="s">
-        <v>18</v>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5" t="s">
@@ -53176,35 +53572,43 @@
       <c r="B70" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>263</v>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
-      <c r="G70" s="4" t="s">
-        <v>17</v>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I70" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M70" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N70" s="5" t="s">
-        <v>269</v>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 19%</t>
+        </is>
       </c>
       <c r="O70" s="5" t="s">
         <v>270</v>
@@ -53217,18 +53621,26 @@
       <c r="B71" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>72</v>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F71" s="6"/>
-      <c r="G71" s="4" t="s">
-        <v>34</v>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H71" s="6" t="n">
         <v>12</v>
@@ -53237,16 +53649,18 @@
         <v>1</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M71" s="6" t="s">
-        <v>18</v>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N71" s="5"/>
       <c r="O71" s="5" t="s">
@@ -53260,37 +53674,47 @@
       <c r="B72" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>49</v>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령 1</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
-      <c r="G72" s="4" t="s">
-        <v>17</v>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I72" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N72" s="5" t="s">
-        <v>275</v>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%, 박자 근사</t>
+        </is>
       </c>
       <c r="O72" s="5" t="s">
         <v>276</v>
@@ -53303,34 +53727,44 @@
       <c r="B73" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>278</v>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령 2</t>
+        </is>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
-      <c r="G73" s="4" t="s">
-        <v>17</v>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M73" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N73" s="5"/>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 21%</t>
+        </is>
+      </c>
       <c r="O73" s="5" t="s">
         <v>279</v>
       </c>
@@ -53342,16 +53776,22 @@
       <c r="B74" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>49</v>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
-      <c r="G74" s="4" t="s">
-        <v>34</v>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H74" s="6" t="n">
         <v>12</v>
@@ -53360,16 +53800,18 @@
         <v>1</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M74" s="6" t="s">
-        <v>18</v>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N74" s="5"/>
       <c r="O74" s="5" t="s">
@@ -53383,34 +53825,44 @@
       <c r="B75" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>281</v>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
-      <c r="G75" s="4" t="s">
-        <v>17</v>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M75" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N75" s="5"/>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 54%, 박자 근사</t>
+        </is>
+      </c>
       <c r="O75" s="5" t="s">
         <v>284</v>
       </c>
@@ -53422,16 +53874,22 @@
       <c r="B76" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>49</v>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청춘가</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
-      <c r="G76" s="4" t="s">
-        <v>34</v>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H76" s="6" t="n">
         <v>12</v>
@@ -53443,15 +53901,21 @@
         <v>96</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N76" s="5"/>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 18%</t>
+        </is>
+      </c>
       <c r="O76" s="5" t="s">
         <v>287</v>
       </c>
@@ -53463,16 +53927,22 @@
       <c r="B77" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>49</v>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쾌지나 칭칭</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
-      <c r="G77" s="4" t="s">
-        <v>34</v>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H77" s="6" t="n">
         <v>12</v>
@@ -53481,18 +53951,24 @@
         <v>1</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N77" s="5"/>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 35%</t>
+        </is>
+      </c>
       <c r="O77" s="5" t="s">
         <v>290</v>
       </c>
@@ -53504,18 +53980,26 @@
       <c r="B78" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>72</v>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태평가</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F78" s="6"/>
-      <c r="G78" s="4" t="s">
-        <v>34</v>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H78" s="6" t="n">
         <v>12</v>
@@ -53527,13 +54011,15 @@
         <v>108</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M78" s="6" t="s">
-        <v>18</v>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N78" s="5"/>
       <c r="O78" s="5" t="s">
@@ -53547,18 +54033,26 @@
       <c r="B79" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>297</v>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통영 개타령</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F#</t>
+        </is>
       </c>
       <c r="F79" s="6"/>
-      <c r="G79" s="4" t="s">
-        <v>17</v>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H79" s="6" t="n">
         <v>16</v>
@@ -53567,20 +54061,20 @@
         <v>1</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N79" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N79" s="5"/>
       <c r="O79" s="5" t="s">
         <v>298</v>
       </c>
@@ -53592,36 +54086,48 @@
       <c r="B80" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>296</v>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년 노래</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
-      <c r="G80" s="4" t="s">
-        <v>17</v>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M80" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N80" s="5"/>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
       <c r="O80" s="5" t="s">
         <v>301</v>
       </c>
@@ -53633,18 +54139,22 @@
       <c r="B81" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>49</v>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E81" s="6"/>
-      <c r="F81" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>34</v>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H81" s="6" t="n">
         <v>12</v>
@@ -53661,8 +54171,10 @@
       <c r="L81" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="6" t="s">
-        <v>18</v>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N81" s="5"/>
       <c r="O81" s="5" t="s">
@@ -53676,18 +54188,26 @@
       <c r="B82" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>72</v>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
       </c>
       <c r="F82" s="6"/>
-      <c r="G82" s="4" t="s">
-        <v>34</v>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H82" s="6" t="n">
         <v>12</v>
@@ -53699,13 +54219,15 @@
         <v>96</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M82" s="6" t="s">
-        <v>18</v>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N82" s="5"/>
       <c r="O82" s="5" t="s">
@@ -53719,16 +54241,22 @@
       <c r="B83" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>49</v>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한강수 타령</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
-      <c r="G83" s="4" t="s">
-        <v>34</v>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H83" s="6" t="n">
         <v>12</v>
@@ -53737,16 +54265,18 @@
         <v>1</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M83" s="6" t="s">
-        <v>18</v>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N83" s="5"/>
       <c r="O83" s="5" t="s">
@@ -53760,36 +54290,48 @@
       <c r="B84" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>49</v>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">함양 양잠가</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
-      <c r="G84" s="4" t="s">
-        <v>27</v>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I84" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N84" s="5"/>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 29%</t>
+        </is>
+      </c>
       <c r="O84" s="5" t="s">
         <v>312</v>
       </c>
@@ -53801,16 +54343,22 @@
       <c r="B85" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>58</v>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
-      <c r="G85" s="4" t="s">
-        <v>34</v>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H85" s="6" t="n">
         <v>12</v>
@@ -53819,19 +54367,23 @@
         <v>1</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L85" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M85" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N85" s="5" t="s">
-        <v>315</v>
+        <v>0</v>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
       </c>
       <c r="O85" s="5" t="s">
         <v>316</v>
@@ -53844,14 +54396,18 @@
       <c r="B86" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>314</v>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
-      <c r="G86" s="4" t="s">
-        <v>34</v>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H86" s="6" t="n">
         <v>12</v>
@@ -53860,20 +54416,20 @@
         <v>1</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K86" s="6" t="n">
         <v>7</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N86" s="5" t="s">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N86" s="5"/>
       <c r="O86" s="5" t="s">
         <v>318</v>
       </c>
@@ -53885,16 +54441,22 @@
       <c r="B87" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>39</v>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">희망가</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
-      <c r="G87" s="4" t="s">
-        <v>34</v>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H87" s="6" t="n">
         <v>12</v>
@@ -53906,13 +54468,15 @@
         <v>96</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M87" s="6" t="s">
-        <v>18</v>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
       </c>
       <c r="N87" s="5"/>
       <c r="O87" s="5" t="s">
@@ -53963,18 +54527,26 @@
       <c r="B89" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>44</v>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">옹헤야</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#→C</t>
+        </is>
       </c>
       <c r="F89" s="6"/>
-      <c r="G89" s="4" t="s">
-        <v>17</v>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H89" s="6" t="n">
         <v>16</v>
@@ -53983,19 +54555,23 @@
         <v>1</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M89" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N89" s="5" t="s">
-        <v>45</v>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
       </c>
       <c r="O89" s="5" t="s">
         <v>46</v>
@@ -54008,18 +54584,26 @@
       <c r="B90" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>53</v>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신고산 타령-2</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
       </c>
       <c r="F90" s="6"/>
-      <c r="G90" s="4" t="s">
-        <v>17</v>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H90" s="6" t="n">
         <v>16</v>
@@ -54031,16 +54615,20 @@
         <v>32</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M90" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N90" s="5" t="s">
-        <v>54</v>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
       </c>
       <c r="O90" s="5" t="s">
         <v>55</v>
@@ -54103,8 +54691,183 @@
         </is>
       </c>
     </row>
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑.csv</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2.csv</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대금키</t>
+        </is>
+      </c>
+      <c r="F93" s="6"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2.csv</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O94"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -54121,7 +54884,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.21"/>
@@ -55234,17 +55997,19 @@
         <v>84</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="N26" s="5" t="s">
-        <v>387</v>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사가 원본과 달랐음). 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 세마치 3/4. 오른쪽부터 7줄(왼쪽 빈 줄). 율명 오른쪽 ^ 꾸밈은 ^ 로 적음, 潢 옆 작은 ○ 는 생략. 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="27" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55276,7 +56041,7 @@
         <v>120</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
@@ -55285,8 +56050,10 @@
       <c r="M27" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="N27" s="5" t="s">
-        <v>389</v>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 한 줄씩 어긋나고 율명도 원본과 달랐음). 손격자, 12정간·굵은 선 3칸마다 → 세마치 3/4. 10줄, 오른쪽부터 줄1. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 화살표, 두 줄은 가사 없음(줄1 = 줄3 가락). 율명 옆 ^ 꾸밈은 ^ 로 적음.</t>
+        </is>
       </c>
     </row>
     <row r="28" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55296,17 +56063,23 @@
       <c r="B28" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>17</v>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매화 타령</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>10</v>
@@ -55315,7 +56088,7 @@
         <v>7</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>9</v>
@@ -55327,8 +56100,10 @@
       <c r="M28" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="N28" s="5" t="s">
-        <v>391</v>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 "&lt; 매화 타령 굿거리 &gt;". 16정간 양식이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개(가운데 굵은 선), 칸마다 율명 3개(굿거리 3소박, 줄5 정간4만 4개) → 큰 칸 하나 = 정간 하나, 4/4·8. 오른쪽부터 줄1, 율명 7줄에 내용(줄7은 정간1~4만), 줄8~10은 빈 인쇄 줄. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 네모와 화살표, 줄2 위 "전주" 화살표, 줄2 정간1 아래 "&lt;전주&gt;", 줄3 위 "&lt;1절&gt;", 줄4 위 "&lt;2절&gt;", 줄5 정간6 아래 "3절" 네모. 줄6 정간7~8에 X표(삭제 표시).</t>
+        </is>
       </c>
     </row>
     <row r="29" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55338,39 +56113,47 @@
       <c r="B29" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>34</v>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽금포 타령</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F29" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N29" s="5" t="s">
-        <v>393</v>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "몽금포 타령  굿거리 (서도소리)". 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 선 3칸마다 → 3/4·12. 격자 오른쪽 끝 2줄은 비어 있고(맨 오른쪽 위 여백에 "※ 요성 격하게" 메모) 그 왼쪽부터 율명 6줄 → 줄1="장산곳" 줄. 가사는 각 율명 줄 오른쪽 칸. 한 장 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="30" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55380,29 +56163,35 @@
       <c r="B30" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>34</v>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물레타령</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F30" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
@@ -55411,50 +56200,64 @@
       <c r="M30" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="N30" s="5" t="s">
-        <v>395</v>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다) → 중모리 3/4·12. 인쇄 줄번호 1·8은 빈 줄이라 제외, 인쇄 2~7 = 줄1~6. 위쪽 묶음: 후렴=인쇄3·2(줄2·1), 1절=5·4(줄4·3), 2절=7·6(줄6·5). 오른쪽 여백 "남도민요 물레타령 중모리". 율명 오른쪽 겹꺾쇠 꾸밈은 ^ 로 적음(하단 범례 ※潢^→潢無 는 본문 밖이라 생략). 괄호 친 (無)는 無 로 적고 비고. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>34</v>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_밀양 아리랑.tsv</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밀양 아리랑</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F31" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="N31" s="5" t="s">
-        <v>397</v>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 밀양 아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 오른쪽 4줄은 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
+        </is>
       </c>
     </row>
     <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55464,23 +56267,29 @@
       <c r="B32" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>17</v>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>32</v>
@@ -55495,8 +56304,10 @@
       <c r="M32" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="N32" s="5" t="s">
-        <v>399</v>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "서도민요 박연폭포 '굿거리, 전주'". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 오른쪽 4줄만 내용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 줄1·3, 줄2·4 가락이 거의 같음. 無 뒤 작은 점은 글자 획으로 보고 생략. 줄2 정간5 율명·가사 먹 번짐.</t>
+        </is>
       </c>
     </row>
     <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55506,17 +56317,23 @@
       <c r="B33" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>17</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느리게</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>4</v>
@@ -55525,10 +56342,10 @@
         <v>4</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
@@ -55537,8 +56354,10 @@
       <c r="M33" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="N33" s="5" t="s">
-        <v>401</v>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "박연폭포 "체라" (느리게)" 아래 "정악" 표시. 한 곡. 한 줄에 큰 칸 8개(인쇄 정간 2개씩 합친 칸, 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸. 오른쪽 4줄만 사용, 왼쪽 열은 빈 양식. 칸 끝 작은 세모는 △(쉼). 줄4 정간4·5 경계 왼쪽에 &lt; 표시.</t>
+        </is>
       </c>
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55548,29 +56367,35 @@
       <c r="B34" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>34</v>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뱃노래</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F34" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
@@ -55579,8 +56404,10 @@
       <c r="M34" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N34" s="5" t="s">
-        <v>403</v>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^.</t>
+        </is>
       </c>
     </row>
     <row r="35" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55590,14 +56417,20 @@
       <c r="B35" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>34</v>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베틀가</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F35" s="6" t="n">
         <v>12</v>
@@ -55612,17 +56445,19 @@
         <v>48</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="N35" s="5" t="s">
-        <v>405</v>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀.</t>
+        </is>
       </c>
     </row>
     <row r="36" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55632,14 +56467,20 @@
       <c r="B36" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>34</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">북간도 아리랑</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F36" s="6" t="n">
         <v>12</v>
@@ -55651,10 +56492,10 @@
         <v>8</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
@@ -55663,8 +56504,10 @@
       <c r="M36" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="N36" s="5" t="s">
-        <v>407</v>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 줄 번호 1~8(오른쪽부터), 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "북간도 아리랑 중모리", 상단 "정악/산조". 줄 위 표기: 줄1~2 후렴, 줄3~4 1절, 줄5~6 2절, 줄7~8 후렴(한 곡). 율명 옆·아래 사선 꾸밈은 ／, 南 옆 작은 꺾쇠는 ^. 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55674,15 +56517,19 @@
       <c r="B37" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>154</v>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가</t>
+        </is>
       </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="4" t="s">
-        <v>27</v>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>4</v>
@@ -55691,10 +56538,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
@@ -55703,8 +56550,10 @@
       <c r="M37" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="N37" s="5" t="s">
-        <v>409</v>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="38" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55714,29 +56563,35 @@
       <c r="B38" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>34</v>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사철가</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
@@ -55745,8 +56600,10 @@
       <c r="M38" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="N38" s="5" t="s">
-        <v>411</v>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시.</t>
+        </is>
       </c>
     </row>
     <row r="39" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55756,17 +56613,23 @@
       <c r="B39" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>27</v>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사철가</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>5</v>
@@ -55775,10 +56638,10 @@
         <v>5</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
@@ -55787,8 +56650,10 @@
       <c r="M39" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="N39" s="5" t="s">
-        <v>413</v>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(줄 번호 8→1, 정간 번호 1~16, 하단 "- 196 -")이지만 가로선이 번호 2개(1·2, 3·4 …)마다만 있고 큰 칸 8개에 율명이 2~4개씩 쌓여 있어 큰 칸 하나 = 정간 하나, 4/4·8로 적음(율명은 칸 안 위→아래, 나란히 쓴 두 글자는 붙임). 내용은 오른쪽 1~5줄, 6~8줄 빈 줄. 오른쪽 여백 세로 "경기민요 사철가 굿거리". 줄1~2 위 괄호로 "후렴"(?) 표시, 줄3 위 "전주" 표시 — 줄1~2(지화자/종네 … 종을씨구우나)가 후렴, 줄3~5가 본 노래로 보임(한 곡). 율명 아래 작은 점 두 개(위는 짧은 획처럼 보이기도 함)는 ⁚ 로 통일. 가사 "종"은 "좋"일 수 있음(글자 모양은 종).</t>
+        </is>
       </c>
     </row>
     <row r="40" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55798,17 +56663,23 @@
       <c r="B40" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>27</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상사 천리몽</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>4</v>
@@ -55817,10 +56688,10 @@
         <v>4</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
@@ -55829,8 +56700,10 @@
       <c r="M40" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="N40" s="5" t="s">
-        <v>415</v>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식 위에 손으로 큰 칸을 그림: 인쇄 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 인쇄 줄 2~5번(오른쪽 4줄)에 내용, 인쇄 1번·6~8번 줄은 빔. 가사는 각 율명 줄 바로 오른쪽 칸. 南 흘림이 古처럼 보이는 곳은 南으로 적음. 줄2 정간3·정간7 / 줄3 정간3 가사 칸에 '후' 옆 곡선(괄호·화살표) 표시 있음.</t>
+        </is>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55840,18 +56713,22 @@
       <c r="B41" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>166</v>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상주 모심기</t>
+        </is>
       </c>
       <c r="D41" s="5"/>
-      <c r="E41" s="4" t="s">
-        <v>34</v>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F41" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>4</v>
@@ -55869,8 +56746,10 @@
       <c r="M41" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="N41" s="5" t="s">
-        <v>417</v>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 3/4. 내용은 오른쪽 4줄, 왼쪽 빈 줄은 뺌. 1줄 가사 칸 오른쪽 바깥에 "(상주 모심기)"(4~6정간), "(중모리)"(7~9정간) 표기(율명 아님). 여러 칸의 긴 물결선(요성)은 생략. 검은 사각형은 정정 종이를 붙여 다시 쓴 칸으로, 흰 획 글자를 판독. 1·3줄 7~12정간, 2·4줄은 같은 가락.</t>
+        </is>
       </c>
     </row>
     <row r="42" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55880,14 +56759,20 @@
       <c r="B42" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>34</v>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 타령</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F42" s="6" t="n">
         <v>12</v>
@@ -55899,20 +56784,22 @@
         <v>10</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="N42" s="5" t="s">
-        <v>419</v>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 가로선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 한 곡. 상단에 "새타령(굿거리) 1", "C#key⟷6판 c key / 정악 청" 메모. 율명 옆 작은 ^ 꾸밈은 ^ 로 적음. 潢 아래 無를 쓴 칸(潢|無)의 요성 곡선·10줄 11정간의 ○ 묶음은 생략. 12정간 끝의 D·○ 모양 표시는 쉼 △ 로 적음. 氵 보이는 女古는 㴌, 氵 없는 것은 姑로 구분. 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55922,20 +56809,26 @@
       <c r="B43" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>34</v>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">새 타령-2</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2절</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H43" s="6" t="n">
         <v>11</v>
@@ -55944,7 +56837,7 @@
         <v>111</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
@@ -55953,8 +56846,10 @@
       <c r="M43" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="N43" s="5" t="s">
-        <v>421</v>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다) → 3/4·12. 상단 "&lt;2절&gt; 새타령(2) C#키⟷C키". 오른쪽부터 11줄(11줄은 왼쪽 테두리 밖 여백에 율명, 테두리 안 좁은 칸에 가사). 한 곡. 4줄 3~11정간 세로 연음선, 5줄 10~11정간 세로 물결선만 있어 비움. 潢|無 칸의 요성 물결선 생략. 潕 옆 C·&lt; 모양 꾸밈과 㴌·南 옆 ^ 꾸밈은 ^ 로 적음. 4줄 2정간 淋 아래 작은 물결 표시 생략.</t>
+        </is>
       </c>
     </row>
     <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55964,14 +56859,20 @@
       <c r="B44" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>34</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">석별가</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F44" s="6" t="n">
         <v>12</v>
@@ -55983,10 +56884,10 @@
         <v>6</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
@@ -55995,8 +56896,10 @@
       <c r="M44" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="N44" s="5" t="s">
-        <v>423</v>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 원본과 달랐음). 인쇄 12정간 양식, 굵은 선 3칸마다 → 3/4. 오른쪽부터 6줄(7·8줄 빔). 가사는 각 율명 줄 오른쪽 칸. 정간12 의 ―와 ▷ 모양은 ―|△ 로 적음. 율명 오른쪽 ^ 꾸밈은 ^ 로 적음.</t>
+        </is>
       </c>
     </row>
     <row r="45" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56006,29 +56909,35 @@
       <c r="B45" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>17</v>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선화공주</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F45" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
@@ -56037,8 +56946,10 @@
       <c r="M45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="N45" s="5" t="s">
-        <v>425</v>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="46" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56048,17 +56959,23 @@
       <c r="B46" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>17</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신 만고강산</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남도민요</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>6</v>
@@ -56067,10 +56984,10 @@
         <v>6</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -56079,8 +56996,10 @@
       <c r="M46" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="N46" s="8" t="s">
-        <v>427</v>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="47" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56090,26 +57009,32 @@
       <c r="B47" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>17</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신 천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>4</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>2</v>
@@ -56121,8 +57046,10 @@
       <c r="M47" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="N47" s="5" t="s">
-        <v>429</v>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시.</t>
+        </is>
       </c>
     </row>
     <row r="48" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56132,17 +57059,23 @@
       <c r="B48" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>17</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신고산 타령</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>5</v>
@@ -56151,10 +57084,10 @@
         <v>5</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
@@ -56163,8 +57096,10 @@
       <c r="M48" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N48" s="8" t="s">
-        <v>431</v>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(번호 1~16)에 번호 2개씩 걸친 큰 칸 8개, 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 8정간 4/4(굿거리). 오른쪽 여백 제목 "신고산 타령"/부제 "굿거리", 줄1·2 위 "후렴" 묶음. 내용 있는 줄은 오른쪽 1~5줄(6~8줄 빈 줄 제외), 줄5는 정간4까지(정간3~4에 긴 사선). 가사는 각 율명 줄 오른쪽 칸. 율명 오른쪽 작은 ^ 꾸밈은 ^ 로 적음.</t>
+        </is>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56174,14 +57109,20 @@
       <c r="B49" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>34</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단가 중모리</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F49" s="6" t="n">
         <v>12</v>
@@ -56193,10 +57134,10 @@
         <v>8</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
@@ -56205,8 +57146,10 @@
       <c r="M49" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="N49" s="8" t="s">
-        <v>433</v>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~8 줄, 1~12 정간), 12정간·굵은 선 3칸마다 → 3/4·12, 8줄 모두 사용, 한 곡. 오른쪽 여백 '1. (쑥대머리) 단가, 중모리'. 이전 판독의 淋·淋潢 은 대부분 氵姑(㴌). 潢 오른쪽 아래 겹 곡선 ')' 꾸밈은 潢^ 로 적음 — 하단 메모칸 '※ 潢) ⇒ 潢 아래 無(곡선)' 즉 潢에서 無로 꺾어 내리는 표시. 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="50" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56216,29 +57159,35 @@
       <c r="B50" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>34</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쑥대머리</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F50" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -56247,8 +57196,10 @@
       <c r="M50" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="N50" s="8" t="s">
-        <v>435</v>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다), 5줄 사용(6~8줄 빈칸). 오른쪽 여백 "&lt;ス&gt;" 쑥대머리 중모리. 潢 뒤 이중 곡선 꼬리는 ^ 로 표기 — 하단 메모 "※ 潢(꼬리) ⇒ 潢→無"(꼬리 = 無로 흘러내림 표시). (無)는 괄호 친 無. "- 197 -"는 양식 용지 번호.</t>
+        </is>
       </c>
     </row>
     <row r="51" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56258,27 +57209,31 @@
       <c r="B51" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>201</v>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑 낭낭</t>
+        </is>
       </c>
       <c r="D51" s="5"/>
-      <c r="E51" s="4" t="s">
-        <v>17</v>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F51" s="6" t="n">
         <v>16</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
@@ -56287,8 +57242,10 @@
       <c r="M51" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="N51" s="8" t="s">
-        <v>437</v>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움).</t>
+        </is>
       </c>
     </row>
     <row r="52" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56298,14 +57255,20 @@
       <c r="B52" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>17</v>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑 목동</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F52" s="6" t="n">
         <v>16</v>
@@ -56320,7 +57283,7 @@
         <v>80</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
@@ -56329,8 +57292,10 @@
       <c r="M52" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="N52" s="5" t="s">
-        <v>439</v>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|―율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략.</t>
+        </is>
       </c>
     </row>
     <row r="53" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56340,29 +57305,35 @@
       <c r="B53" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>17</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">애수의 가을밤</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F53" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>6</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0</v>
@@ -56371,8 +57342,10 @@
       <c r="M53" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="N53" s="8" t="s">
-        <v>441</v>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key.</t>
+        </is>
       </c>
     </row>
     <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56382,14 +57355,20 @@
       <c r="B54" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>34</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야월삼경</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F54" s="6" t="n">
         <v>12</v>
@@ -56401,10 +57380,10 @@
         <v>8</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
@@ -56413,8 +57392,10 @@
       <c r="M54" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="N54" s="5" t="s">
-        <v>443</v>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 오른쪽 상단 "야월삼경 &lt;중모리&gt; C#키". 12정간, 굵은 선 3칸마다 → 3/4. 오른쪽 맨 끝 빈 칸 제외, 오른쪽부터 8줄 사용(왼쪽 2칸 빈 줄). 가사는 각 율명 줄 오른쪽 칸. 정간 안 짧은 가로선·작은 사선 점은 모두 ― 로 적음. 줄3·줄5 등 청성(㴌·㳞·湳) 가락 반복. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="55" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56424,14 +57405,20 @@
       <c r="B55" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>34</v>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양류가</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F55" s="6" t="n">
         <v>12</v>
@@ -56443,10 +57430,10 @@
         <v>4</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
@@ -56455,40 +57442,52 @@
       <c r="M55" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="N55" s="8" t="s">
-        <v>445</v>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="56" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>34</v>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_양류가.tsv</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양류가</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F56" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
@@ -56497,8 +57496,10 @@
       <c r="M56" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="N56" s="5" t="s">
-        <v>447</v>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 양류가(굿거리). 오른쪽 4줄은 구 아리랑-2. 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
+        </is>
       </c>
     </row>
     <row r="57" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56508,29 +57509,35 @@
       <c r="B57" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>34</v>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">양산도</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F57" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
@@ -56539,8 +57546,10 @@
       <c r="M57" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="N57" s="5" t="s">
-        <v>449</v>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 ―·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네..</t>
+        </is>
       </c>
     </row>
     <row r="58" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56550,29 +57559,35 @@
       <c r="B58" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>34</v>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">영천 아리랑</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K58" s="6" t="n">
         <v>0</v>
@@ -56581,40 +57596,52 @@
       <c r="M58" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="N58" s="5" t="s">
-        <v>451</v>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자: 한 줄에 큰 칸 8개(칸 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4(근사, 원본 표기는 세마치). 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사 칸의 &lt; 표시(쓰라·영·아리랑·고·날·산·큰 앞)는 바로 위 정간 끝에 ‹ 로 적음. 南 옆 작은 꺾쇠는 ^.</t>
+        </is>
       </c>
     </row>
     <row r="59" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>34</v>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_오봉산 타령.tsv</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오봉산 타령</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F59" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K59" s="6" t="n">
         <v>0</v>
@@ -56623,8 +57650,10 @@
       <c r="M59" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="N59" s="5" t="s">
-        <v>453</v>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 오봉산 타령 굿거리. 오른쪽 4줄은 사발가-2. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="60" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56634,12 +57663,16 @@
       <c r="B60" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>232</v>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">옹이</t>
+        </is>
       </c>
       <c r="D60" s="5"/>
-      <c r="E60" s="4" t="s">
-        <v>34</v>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F60" s="6" t="n">
         <v>12</v>
@@ -56651,10 +57684,10 @@
         <v>10</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>0</v>
@@ -56663,8 +57696,10 @@
       <c r="M60" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="N60" s="5" t="s">
-        <v>455</v>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(번호 없음), 12정간 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 줄1은 전주(가사 없음, 위에 '전주' 글씨). 줄2~9는 8정간까지만 쓰고 끝에 ―|△, 줄10만 12정간까지. 칸 안 짧은 가로선은 ―로 적음. 머리 '옹이', '조창건', 오른쪽 위 채보 메모, 줄10 왼쪽 여백·위에 작은 메모 있음(생략).</t>
+        </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56674,39 +57709,47 @@
       <c r="B61" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>34</v>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울산 아가씨</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F61" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="N61" s="8" t="s">
-        <v>457</v>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|―?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음.</t>
+        </is>
       </c>
     </row>
     <row r="62" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56716,29 +57759,35 @@
       <c r="B62" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>17</v>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별가</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느릿 굿거리</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G62" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J62" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I62" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>15</v>
       </c>
       <c r="K62" s="6" t="n">
         <v>0</v>
@@ -56747,8 +57796,10 @@
       <c r="M62" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="N62" s="5" t="s">
-        <v>459</v>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(196)이지만 번호 2개(1·2,3·4…)씩 큰 칸 8개로 쓰고 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개, 4/4·8(는실 타령 양식). 맨 오른쪽 인쇄 열(1)은 비어 열2를 줄1로, 열2~5 = 줄1~4, 열6~8 빈 줄 제외. 오른쪽 여백에 "이별가", "느릿 굿거리", "노래따라". 율명 오른쪽 작은 3자·s자 꾸밈(汰·潢·南 등)과 칸 사이 세로 물결선·닫는 곡선 요성 표시는 기호표에 없어 생략, 꺾쇠 모양만 ^. 가사 칸의 늘임 ㅣ 는 생략. 멜리스마 모음(아·이)이 가사로 붙음.</t>
+        </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56758,29 +57809,35 @@
       <c r="B63" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>34</v>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후렴</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0</v>
@@ -56789,8 +57846,10 @@
       <c r="M63" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="N63" s="8" t="s">
-        <v>461</v>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56800,14 +57859,20 @@
       <c r="B64" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>34</v>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전라도 산타령</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F64" s="6" t="n">
         <v>12</v>
@@ -56822,7 +57887,7 @@
         <v>47</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0</v>
@@ -56831,8 +57896,10 @@
       <c r="M64" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="N64" s="5" t="s">
-        <v>463</v>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="65" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56844,8 +57911,10 @@
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
-      <c r="E65" s="4" t="s">
-        <v>34</v>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F65" s="6" t="n">
         <v>12</v>
@@ -56860,7 +57929,7 @@
         <v>17</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0</v>
@@ -56869,8 +57938,10 @@
       <c r="M65" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="N65" s="5" t="s">
-        <v>465</v>
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 없는 손채보, 손으로 그린 격자(번호 없음), 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽 끝 열은 비어 있어 그 왼쪽 율명 열을 줄1로 셈. 내용은 2줄뿐(나머지 왼쪽 줄은 빈 칸). 줄2는 율명 없이 세로·사선 획과 세모만 있음(장구 등 반주 표시로 보임) — 기호표에 없어 모두 ﾉ 로 적고 비고에 모양. 가사: 깐다 깐다 정든 님이 떠나간다.</t>
+        </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56880,20 +57951,26 @@
       <c r="B66" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>34</v>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령 / 닐리리야</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리 / 굿거리</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F66" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>7</v>
@@ -56902,7 +57979,7 @@
         <v>84</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0</v>
@@ -56911,8 +57988,10 @@
       <c r="M66" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="N66" s="5" t="s">
-        <v>467</v>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑.</t>
+        </is>
       </c>
     </row>
     <row r="67" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56922,14 +58001,20 @@
       <c r="B67" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>34</v>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령 / 담바귀 타령</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리 / 굿거리</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F67" s="6" t="n">
         <v>12</v>
@@ -56944,7 +58029,7 @@
         <v>95</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0</v>
@@ -56953,8 +58038,10 @@
       <c r="M67" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="N67" s="5" t="s">
-        <v>469</v>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南.</t>
+        </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56964,14 +58051,20 @@
       <c r="B68" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>34</v>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">멜로디버전</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F68" s="6" t="n">
         <v>12</v>
@@ -56986,17 +58079,19 @@
         <v>119</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="N68" s="5" t="s">
-        <v>471</v>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12, 10줄. 각 율명 열 오른쪽 가사 칸은 모두 비어 있음(멜로디만). 짝수 줄(2·4·8·10)은 거의 같은 南/無南/無潢/仲姑 가락 반복, 3·7줄 동일. 5·6줄 가운데 잉크 번짐. 이전 판독의 姑/僙 대부분은 南/姑의 오독이라 정정.</t>
+        </is>
       </c>
     </row>
     <row r="69" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57006,14 +58101,20 @@
       <c r="B69" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>34</v>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F69" s="6" t="n">
         <v>12</v>
@@ -57028,7 +58129,7 @@
         <v>113</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0</v>
@@ -57037,8 +58138,10 @@
       <c r="M69" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="N69" s="5" t="s">
-        <v>473</v>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 ― 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △.</t>
+        </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="73.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57048,15 +58151,19 @@
       <c r="B70" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>263</v>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="4" t="s">
-        <v>17</v>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>4</v>
@@ -57065,10 +58172,10 @@
         <v>4</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K70" s="6" t="n">
         <v>0</v>
@@ -57077,8 +58184,10 @@
       <c r="M70" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="N70" s="5" t="s">
-        <v>475</v>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만.</t>
+        </is>
       </c>
     </row>
     <row r="71" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57088,14 +58197,20 @@
       <c r="B71" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>34</v>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F71" s="6" t="n">
         <v>12</v>
@@ -57107,10 +58222,10 @@
         <v>10</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>0</v>
@@ -57119,8 +58234,10 @@
       <c r="M71" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="N71" s="5" t="s">
-        <v>477</v>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 제목 "창부타령 1 굿거리", 오른쪽 위 "C#키"·"1절". 오른쪽부터 10줄, 가사는 각 율명 줄 오른쪽 좁은 칸. 흘림 南(十+冂)·姑(女古)를 구별, 氵仲(神 모양)=㳞, 氵姑=㴌, 氵南=湳. 한 칸에 위아래로 쌓인 두 글자는 |로 구분. 줄1은 시작 '아아니'와 각 장 끝 '이' 받침 가락. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="72" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57130,17 +58247,23 @@
       <c r="B72" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>17</v>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령 1</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>8</v>
@@ -57149,10 +58272,10 @@
         <v>8</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>0</v>
@@ -57161,8 +58284,10 @@
       <c r="M72" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="N72" s="5" t="s">
-        <v>479</v>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 196)이나 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 2~4개씩 세로로 적힘 → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 8줄 모두 사용, 가사는 각 율명 열 바로 오른쪽 칸. 한 곡: 줄1 '아니 아니 노지는 못하리라' 후렴, 줄2~7 1절(우연히 길을 갈 적에…, 줄7 후반 후렴 반복), 줄8 위 '?절'(2절?) 표기 후 '백구야 날지 마라…'. 古처럼 흘린 글자 중 다리가 있는 것은 南, 女변이 있는 것은 姑. 神처럼 쓴 氵仲은 㳞, 氵 하나로 이어 쓴 '神姑'는 㳞㴌으로 적음. 가사 칸의 ㅣ(늘임)·&lt; 표시는 생략.</t>
+        </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57172,15 +58297,19 @@
       <c r="B73" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>278</v>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령 2</t>
+        </is>
       </c>
       <c r="D73" s="5"/>
-      <c r="E73" s="4" t="s">
-        <v>17</v>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>8</v>
@@ -57189,10 +58318,10 @@
         <v>8</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0</v>
@@ -57201,8 +58330,10 @@
       <c r="M73" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="N73" s="5" t="s">
-        <v>481</v>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 번호 196)이지만 번호 2개(1·2, 3·4 …)마다 굵은 선으로 묶인 큰 칸 8개에 율명이 3~4개씩 쌓인 양식 → 큰 칸 하나 = 정간 하나, 4/4·8. 율명은 칸 안 위→아래로 | 로 이어 씀. 오른쪽부터 8줄 모두 사용, 한 곡. 상단 줄5·6 위에 '3절 | 2절끝' 메모. 가사는 각 율명 줄 오른쪽 칸. 1줄 8정간(15·16)은 큰 X 지움표로 비어 있음. 女변 古형은 姑, 十+冂형은 南(氵 붙으면 湳). 같은 높이 나란히 쓴 두 음(㳞㴌, 無南, 仲姑 등)은 붙여 씀.</t>
+        </is>
       </c>
     </row>
     <row r="74" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57212,14 +58343,20 @@
       <c r="B74" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>34</v>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F74" s="6" t="n">
         <v>12</v>
@@ -57231,10 +58368,10 @@
         <v>6</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0</v>
@@ -57243,8 +58380,10 @@
       <c r="M74" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="N74" s="5" t="s">
-        <v>483</v>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐.</t>
+        </is>
       </c>
     </row>
     <row r="75" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57254,27 +58393,31 @@
       <c r="B75" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>281</v>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="4" t="s">
-        <v>17</v>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F75" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0</v>
@@ -57283,8 +58426,10 @@
       <c r="M75" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="N75" s="5" t="s">
-        <v>485</v>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호.</t>
+        </is>
       </c>
     </row>
     <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57294,14 +58439,20 @@
       <c r="B76" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>34</v>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청춘가</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F76" s="6" t="n">
         <v>12</v>
@@ -57316,7 +58467,7 @@
         <v>96</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0</v>
@@ -57325,8 +58476,10 @@
       <c r="M76" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="N76" s="5" t="s">
-        <v>487</v>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 오른쪽 여백에 세로로 "청춘가 굿거리". 가사는 각 율명 줄 오른쪽 칸. 1절(줄1~4) 이팔은 청춘에 소년 몸 되어서 문명의 학문을 닦아 봅시다, 2절(줄5~8) 청춘 홍안을 (네) 자랑 마라 덧없는 세월에 백발이 되누나 — 같은 가락 두 번(줄1~4 ≒ 줄5~8, 청성 위주로 약간 다름). 줄4 정간1~3 가사 칸은 지운 흔적. 南 오른쪽 작은 꺾쇠는 ^.</t>
+        </is>
       </c>
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57336,29 +58489,35 @@
       <c r="B77" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>34</v>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쾌지나 칭칭</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F77" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K77" s="6" t="n">
         <v>0</v>
@@ -57367,8 +58526,10 @@
       <c r="M77" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="N77" s="8" t="s">
-        <v>489</v>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
       </c>
     </row>
     <row r="78" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57378,14 +58539,20 @@
       <c r="B78" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>34</v>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">태평가</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F78" s="6" t="n">
         <v>12</v>
@@ -57400,7 +58567,7 @@
         <v>108</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0</v>
@@ -57409,8 +58576,10 @@
       <c r="M78" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="N78" s="5" t="s">
-        <v>491</v>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략.</t>
+        </is>
       </c>
     </row>
     <row r="79" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57420,14 +58589,20 @@
       <c r="B79" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>17</v>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통영 개타령</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F79" s="6" t="n">
         <v>16</v>
@@ -57439,20 +58614,22 @@
         <v>4</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="N79" s="5" t="s">
-        <v>493</v>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無―仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="80" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57462,29 +58639,35 @@
       <c r="B80" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>17</v>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년 노래</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0</v>
@@ -57493,8 +58676,10 @@
       <c r="M80" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="N80" s="5" t="s">
-        <v>495</v>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 큰 칸 양식: 한 줄에 큰 칸 8개(굵은 가로선 2칸마다, 칸 안 점선으로 3소박), 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 율명 위→아래 | 로 4/4·8(근사). 율명 10줄(오른쪽 4줄 + 가운데 겹선 + 왼쪽 6줄), 오른쪽=1. 가사는 각 율명 줄 오른쪽 칸. 머리 "자즌모리 &lt;그정을 1박으로&gt;", 왼쪽 위 "간주는 6박". 줄1·5 일부는 가사 없는 반주성 줄. 하단 "+4" 용지 번호 무시. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57504,14 +58689,20 @@
       <c r="B81" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>34</v>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F81" s="6" t="n">
         <v>12</v>
@@ -57535,8 +58726,10 @@
       <c r="M81" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="N81" s="5" t="s">
-        <v>497</v>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 번호 1~8, 정간 번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 왼쪽 빈 줄 1개 제외. 가사는 각 율명 줄 오른쪽 칸. 줄3·줄7 6정간 아래 경계에 &lt; 표시(‹). 줄2·줄6 12정간 아래 글자는 亻黃(僙)로 판독.</t>
+        </is>
       </c>
     </row>
     <row r="82" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57546,14 +58739,20 @@
       <c r="B82" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>34</v>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F82" s="6" t="n">
         <v>12</v>
@@ -57568,7 +58767,7 @@
         <v>96</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>0</v>
@@ -57577,8 +58776,10 @@
       <c r="M82" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="N82" s="5" t="s">
-        <v>499</v>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 '풍년가 (굿거리)', 오른쪽 위 C#key. 인쇄 양식 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽부터 8줄 사용(왼쪽 2줄 빈 줄 제외). 줄1~4 1절(풍년이 왔네…금수강산으로), 줄5~8 2절(얼씨구나 좋다…화전놀이를 가세)로 같은 가락 반복. 연음 짧은 가로/사선 획은 ―, 아주 작은 점은 ·. 줄4 정간11 체크(✓)는 ^ 로 적음. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57588,14 +58789,20 @@
       <c r="B83" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>34</v>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한강수 타령</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F83" s="6" t="n">
         <v>12</v>
@@ -57607,10 +58814,10 @@
         <v>8</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K83" s="6" t="n">
         <v>0</v>
@@ -57619,8 +58826,10 @@
       <c r="M83" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="N83" s="5" t="s">
-        <v>501</v>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식 12정간(굵은 선 3칸마다, 줄 번호 1~8), 8줄 모두 사용. 오른쪽 여백에 세로로 "한강수 타령 굿거리" 표기. 줄5~8은 후렴(에헤 에헤요 얼삼마 둥개디어라 내사랑아). 가사는 각 율명 줄 오른쪽 칸. 하단 "- 197 -"은 양식 용지 번호.</t>
+        </is>
       </c>
     </row>
     <row r="84" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57630,29 +58839,35 @@
       <c r="B84" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>27</v>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">함양 양잠가</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>4</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K84" s="6" t="n">
         <v>0</v>
@@ -57661,8 +58876,10 @@
       <c r="M84" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="N84" s="8" t="s">
-        <v>503</v>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 양식은 16정간이나 손으로 번호 2개(1·2…)마다 굵은 선을 그어 큰 칸 8개, 칸마다 율명 2~4개(굿거리) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 1열은 비어 있어 인쇄 2열=줄1, 3열=줄2, 4열=줄3, 5열=줄4; 6~8열 빈 줄. 상단 "3후렴→2", "노래 5→4". 줄2는 정간5부터 비어 있음. 하단 메모 "※潢) → 僙에서 無까지 회성" — 潢無) 등 ) 표시는 회성. 오른쪽 여백 제목 "함양 양잠가 굿거리". 古 모양(十+冂)=南, 女+古=姑, 氵+姑=㴌로 구별.</t>
+        </is>
       </c>
     </row>
     <row r="85" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57672,14 +58889,20 @@
       <c r="B85" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>34</v>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F85" s="6" t="n">
         <v>12</v>
@@ -57691,20 +58914,22 @@
         <v>8</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="N85" s="8" t="s">
-        <v>505</v>
+      <c r="N85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'.</t>
+        </is>
       </c>
     </row>
     <row r="86" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57714,12 +58939,16 @@
       <c r="B86" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>314</v>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="4" t="s">
-        <v>34</v>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F86" s="6" t="n">
         <v>12</v>
@@ -57731,20 +58960,22 @@
         <v>7</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>7</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="N86" s="5" t="s">
-        <v>507</v>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(위 줄 번호 1~8, 왼쪽 정간 번호 1~12), 12정간·굵은 선 3칸마다 → 3/4·12. 내용은 오른쪽 7줄(줄8 빈 줄 제외). 오른쪽 여백에 "2절", "흥타령" 표기 — 한 곡. 가사는 각 율명 줄 오른쪽 좁은 칸. 율명 오른쪽 곡선 꾸밈( )) 모양)은 ^ 로 적음. 하단 "- 197 -"은 양식 번호.</t>
+        </is>
       </c>
     </row>
     <row r="87" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57754,14 +58985,20 @@
       <c r="B87" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>34</v>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">희망가</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F87" s="6" t="n">
         <v>12</v>
@@ -57776,7 +59013,7 @@
         <v>96</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K87" s="6" t="n">
         <v>0</v>
@@ -57785,8 +59022,10 @@
       <c r="M87" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="N87" s="5" t="s">
-        <v>509</v>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다, 하단 - 197 -) → 3/4·12, 오른쪽부터 8줄(제목 옆 '중모리'). 가사는 각 율명 줄 오른쪽 칸. 侑 모양은 㑲(亻南)로 적음. 無·㒇 위 작은 v/∪ 꾸밈은 ^ 로. 짧은 사선 획은 ―, 둥근 점은 · 로 구분. 가사 칸의 점 표시는 생략. 한 곡.</t>
+        </is>
       </c>
     </row>
     <row r="88" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57845,8 +59084,176 @@
         </is>
       </c>
     </row>
+    <row r="89" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_아리랑.tsv</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑.csv</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 본조 아리랑(제목 열 "아리랑(세마치)"). 왼쪽 4줄은 밀양 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_구 아리랑-2.tsv</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2.csv</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 구 아리랑 &lt;늦 중모리&gt;. 왼쪽 4줄은 양류가 (채보3). 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_사발가-2.tsv</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2.csv</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 사발가 굿거리. 왼쪽 4줄은 오봉산 타령. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N88"/>
+  <autoFilter ref="A1:N91"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -51762,8 +51762,10 @@
         </is>
       </c>
       <c r="N34" s="5"/>
-      <c r="O34" s="5" t="s">
-        <v>145</v>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
+        </is>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51815,8 +51817,10 @@
           <t xml:space="preserve">한 장에 두 곡</t>
         </is>
       </c>
-      <c r="O35" s="5" t="s">
-        <v>149</v>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+        </is>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51864,8 +51868,10 @@
         </is>
       </c>
       <c r="N36" s="5"/>
-      <c r="O36" s="5" t="s">
-        <v>152</v>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
+        </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51909,8 +51915,10 @@
         </is>
       </c>
       <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
-        <v>155</v>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/사발가.png</t>
+        </is>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51962,8 +51970,10 @@
           <t xml:space="preserve">비고 15%</t>
         </is>
       </c>
-      <c r="O38" s="5" t="s">
-        <v>159</v>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+        </is>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52321,8 +52331,10 @@
         </is>
       </c>
       <c r="N45" s="5"/>
-      <c r="O45" s="5" t="s">
-        <v>183</v>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/선화공주.png</t>
+        </is>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52359,7 +52371,7 @@
         <v>47</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>0</v>
@@ -52370,8 +52382,10 @@
         </is>
       </c>
       <c r="N46" s="5"/>
-      <c r="O46" s="5" t="s">
-        <v>187</v>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
+        </is>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52419,8 +52433,10 @@
         </is>
       </c>
       <c r="N47" s="5"/>
-      <c r="O47" s="5" t="s">
-        <v>190</v>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
+        </is>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56361,11 +56377,15 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>402</v>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_뱃노래.tsv</t>
+        </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -56406,16 +56426,20 @@
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="35" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>404</v>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_베틀가.tsv</t>
+        </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -56456,16 +56480,20 @@
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="36" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>406</v>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_북간도 아리랑.tsv</t>
+        </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -56506,16 +56534,20 @@
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 줄 번호 1~8(오른쪽부터), 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "북간도 아리랑 중모리", 상단 "정악/산조". 줄 위 표기: 줄1~2 후렴, 줄3~4 1절, 줄5~6 2절, 줄7~8 후렴(한 곡). 율명 옆·아래 사선 꾸밈은 ／, 南 옆 작은 꺾쇠는 ^. 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 줄 번호 1~8(오른쪽부터), 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "북간도 아리랑 중모리", 상단 "정악/산조". 줄 위 표기: 줄1~2 후렴, 줄3~4 1절, 줄5~6 2절, 줄7~8 후렴(한 곡). 율명 옆·아래 사선 꾸밈은 ／, 南 옆 작은 꺾쇠는 ^. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>408</v>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/사발가.png</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_사발가.tsv</t>
+        </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -56552,16 +56584,20 @@
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="38" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>410</v>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_사철가-경기민요.tsv</t>
+        </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
@@ -56602,7 +56638,7 @@
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -56903,11 +56939,15 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>424</v>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/선화공주.png</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_선화공주.tsv</t>
+        </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
@@ -56948,16 +56988,20 @@
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="46" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>426</v>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_신 만고강산.tsv</t>
+        </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
@@ -56987,7 +57031,7 @@
         <v>47</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -56998,16 +57042,20 @@
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="47" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>428</v>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_신 천안 삼거리.tsv</t>
+        </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
@@ -57048,7 +57096,7 @@
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -52616,23 +52616,25 @@
         <v>48</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
-        </is>
-      </c>
-      <c r="O51" s="5" t="s">
-        <v>203</v>
+          <t xml:space="preserve">비고 19%, 박자 근사</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
+        </is>
       </c>
     </row>
     <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52684,8 +52686,10 @@
           <t xml:space="preserve">박자 근사</t>
         </is>
       </c>
-      <c r="O52" s="5" t="s">
-        <v>206</v>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+        </is>
       </c>
     </row>
     <row r="53" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52741,8 +52745,10 @@
           <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
-      <c r="O53" s="5" t="s">
-        <v>210</v>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
+        </is>
       </c>
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52847,8 +52853,10 @@
           <t xml:space="preserve">비고 20%</t>
         </is>
       </c>
-      <c r="O55" s="5" t="s">
-        <v>217</v>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/양류가.png</t>
+        </is>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52959,8 +52967,10 @@
         </is>
       </c>
       <c r="N57" s="5"/>
-      <c r="O57" s="5" t="s">
-        <v>224</v>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/양산도.png</t>
+        </is>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53169,8 +53179,10 @@
           <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
-      <c r="O61" s="5" t="s">
-        <v>237</v>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53271,8 +53283,10 @@
           <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
-      <c r="O63" s="5" t="s">
-        <v>246</v>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53309,7 +53323,7 @@
         <v>47</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>0</v>
@@ -53320,8 +53334,10 @@
         </is>
       </c>
       <c r="N64" s="5"/>
-      <c r="O64" s="5" t="s">
-        <v>250</v>
+      <c r="O64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
+        </is>
       </c>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57251,11 +57267,15 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>436</v>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_아리랑 낭낭.tsv</t>
+        </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
@@ -57281,7 +57301,7 @@
         <v>48</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
@@ -57292,16 +57312,20 @@
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움). 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="52" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>438</v>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_아리랑 목동.tsv</t>
+        </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
@@ -57342,16 +57366,20 @@
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|―율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|―율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="53" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>440</v>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_애수의 가을밤.tsv</t>
+        </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
@@ -57392,7 +57420,7 @@
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -57447,11 +57475,15 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>444</v>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/양류가.png</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_양류가.tsv</t>
+        </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
@@ -57492,7 +57524,7 @@
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -57551,11 +57583,15 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>448</v>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/양산도.png</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_양산도.tsv</t>
+        </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
@@ -57596,7 +57632,7 @@
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 ―·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네..</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 ―·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네.. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -57751,11 +57787,15 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>456</v>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_울산 아가씨.tsv</t>
+        </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
@@ -57796,7 +57836,7 @@
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|―?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|―?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -57851,11 +57891,15 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>460</v>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_잦은 뱃노리.tsv</t>
+        </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
@@ -57896,16 +57940,20 @@
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>462</v>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_전라도 산타령.tsv</t>
+        </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
@@ -57935,7 +57983,7 @@
         <v>47</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0</v>
@@ -57946,7 +57994,7 @@
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53582,7 +53582,7 @@
         <v>113</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>0</v>
@@ -53593,8 +53593,10 @@
         </is>
       </c>
       <c r="N69" s="5"/>
-      <c r="O69" s="5" t="s">
-        <v>267</v>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53642,8 +53644,10 @@
           <t xml:space="preserve">비고 19%</t>
         </is>
       </c>
-      <c r="O70" s="5" t="s">
-        <v>270</v>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
+        </is>
       </c>
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53846,8 +53850,10 @@
         </is>
       </c>
       <c r="N74" s="5"/>
-      <c r="O74" s="5" t="s">
-        <v>282</v>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+        </is>
       </c>
     </row>
     <row r="75" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53880,7 +53886,7 @@
         <v>24</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>0</v>
@@ -53892,11 +53898,13 @@
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 54%, 박자 근사</t>
-        </is>
-      </c>
-      <c r="O75" s="5" t="s">
-        <v>284</v>
+          <t xml:space="preserve">비고 58%, 박자 근사</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
+        </is>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54001,8 +54009,10 @@
           <t xml:space="preserve">비고 35%</t>
         </is>
       </c>
-      <c r="O77" s="5" t="s">
-        <v>290</v>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+        </is>
       </c>
     </row>
     <row r="78" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54054,8 +54064,10 @@
         </is>
       </c>
       <c r="N78" s="5"/>
-      <c r="O78" s="5" t="s">
-        <v>293</v>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/태평가.png</t>
+        </is>
       </c>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58191,11 +58203,15 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>472</v>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_창부 타령-2.tsv</t>
+        </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
@@ -58225,7 +58241,7 @@
         <v>113</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0</v>
@@ -58236,16 +58252,20 @@
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 ― 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 ― 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="70" customFormat="false" ht="73.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>474</v>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_창부 타령-3.tsv</t>
+        </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
@@ -58282,7 +58302,7 @@
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -58433,11 +58453,15 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>482</v>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_천안 삼거리.tsv</t>
+        </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
@@ -58478,16 +58502,20 @@
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="75" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>484</v>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_천안 삼거리.tsv</t>
+        </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
@@ -58513,7 +58541,7 @@
         <v>24</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0</v>
@@ -58524,7 +58552,7 @@
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -58579,11 +58607,15 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>488</v>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_쾌지나 칭칭.tsv</t>
+        </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
@@ -58624,16 +58656,20 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="78" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>490</v>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/태평가.png</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_태평가.tsv</t>
+        </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
@@ -58674,7 +58710,7 @@
       </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -54119,8 +54119,10 @@
         </is>
       </c>
       <c r="N79" s="5"/>
-      <c r="O79" s="5" t="s">
-        <v>298</v>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
       </c>
     </row>
     <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54429,8 +54431,10 @@
           <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
-      <c r="O85" s="5" t="s">
-        <v>316</v>
+      <c r="O85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58715,11 +58719,15 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>492</v>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_통영 개타령.tsv</t>
+        </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
@@ -58760,7 +58768,7 @@
       </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無―仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無―仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -59015,11 +59023,15 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>504</v>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_흥 타령.tsv</t>
+        </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -59060,7 +59072,7 @@
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -14,8 +14,8 @@
     <sheet name="글자 빈도" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$94</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$91</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$95</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$92</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'확인 필요 글자'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -50202,7 +50202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.74"/>
@@ -53393,17 +53393,19 @@
       <c r="A66" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>255</v>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령.csv</t>
+        </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령 / 닐리리야</t>
+          <t xml:space="preserve">제주도 타령</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리 / 굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E66" s="6"/>
@@ -53420,10 +53422,10 @@
         <v>1</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>0</v>
@@ -53435,11 +53437,13 @@
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 18%, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>258</v>
+          <t xml:space="preserve">비고 19%, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
       </c>
     </row>
     <row r="67" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54914,8 +54918,65 @@
         </is>
       </c>
     </row>
+    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야.csv</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O94"/>
+  <autoFilter ref="A1:O95"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -54932,7 +54993,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.21"/>
@@ -58057,20 +58118,24 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>466</v>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 닐리리야 (제주도 타령).tsv</t>
+        </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령 / 닐리리야</t>
+          <t xml:space="preserve">제주도 타령</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리 / 굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -58082,27 +58147,29 @@
         <v>12</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="5" t="s">
-        <v>255</v>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령.csv</t>
+        </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 오른쪽 줄1~4(검수 내용은 xlsx 가 기준).</t>
         </is>
       </c>
     </row>
@@ -59396,8 +59463,64 @@
         </is>
       </c>
     </row>
+    <row r="92" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 닐리리야 (닐리리야).tsv</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야.csv</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 왼쪽 줄6~8(검수 내용은 xlsx 가 기준).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N91"/>
+  <autoFilter ref="A1:N92"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -14,8 +14,8 @@
     <sheet name="글자 빈도" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$95</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$92</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'곡 목록'!$A$1:$O$96</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">이미지별!$A$1:$N$93</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'확인 필요 글자'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -50202,7 +50202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.74"/>
@@ -53450,17 +53450,19 @@
       <c r="A67" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>259</v>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령-2.csv</t>
+        </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령 / 담바귀 타령</t>
+          <t xml:space="preserve">제주도 타령-2</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리 / 굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E67" s="6"/>
@@ -53477,10 +53479,10 @@
         <v>1</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>0</v>
@@ -53495,8 +53497,10 @@
           <t xml:space="preserve">한 장에 두 곡</t>
         </is>
       </c>
-      <c r="O67" s="5" t="s">
-        <v>261</v>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54975,8 +54979,65 @@
         </is>
       </c>
     </row>
+    <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2.csv</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O95"/>
+  <autoFilter ref="A1:O96"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -54993,7 +55054,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr defaultColWidth="8.0546875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.21"/>
@@ -58174,20 +58235,24 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>468</v>
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 (제주도 타령-2).tsv</t>
+        </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령 / 담바귀 타령</t>
+          <t xml:space="preserve">제주도 타령-2</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리 / 굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -58199,27 +58264,29 @@
         <v>12</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="5" t="s">
-        <v>259</v>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령-2.csv</t>
+        </is>
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 오른쪽 줄1~4.</t>
         </is>
       </c>
     </row>
@@ -59519,8 +59586,64 @@
         </is>
       </c>
     </row>
+    <row r="93" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 (담바귀 타령-2).tsv</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I93" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2.csv</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 왼쪽 줄5~8.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N92"/>
+  <autoFilter ref="A1:N93"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53560,8 +53560,10 @@
       <c r="A69" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>266</v>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령.csv</t>
+        </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
@@ -58385,8 +58387,10 @@
         <v>0</v>
       </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="5" t="s">
-        <v>266</v>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령.csv</t>
+        </is>
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53613,8 +53613,10 @@
       <c r="A70" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>268</v>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부 타령-2.csv</t>
+        </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
@@ -58439,8 +58441,10 @@
         <v>0</v>
       </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="5" t="s">
-        <v>268</v>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부 타령-2.csv</t>
+        </is>
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53666,8 +53666,10 @@
       <c r="A71" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>271</v>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부 타령.csv</t>
+        </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
@@ -58493,8 +58495,10 @@
         <v>0</v>
       </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="5" t="s">
-        <v>271</v>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부 타령.csv</t>
+        </is>
       </c>
       <c r="N71" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53507,8 +53507,10 @@
       <c r="A68" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>262</v>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-3.csv</t>
+        </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
@@ -58337,8 +58339,10 @@
         <v>1</v>
       </c>
       <c r="L68" s="5"/>
-      <c r="M68" s="5" t="s">
-        <v>262</v>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-3.csv</t>
+        </is>
       </c>
       <c r="N68" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53617,7 +53617,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부 타령-2.csv</t>
+          <t xml:space="preserve">창부타령-4.csv</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -58449,7 +58449,7 @@
       <c r="L70" s="5"/>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부 타령-2.csv</t>
+          <t xml:space="preserve">창부타령-4.csv</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr">

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53670,7 +53670,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부 타령.csv</t>
+          <t xml:space="preserve">창부타령-5.csv</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -58501,7 +58501,7 @@
       <c r="L71" s="5"/>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부 타령.csv</t>
+          <t xml:space="preserve">창부타령-5.csv</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr">

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53825,8 +53825,10 @@
       <c r="A74" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>280</v>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
+        </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
@@ -58651,8 +58653,10 @@
         <v>0</v>
       </c>
       <c r="L74" s="5"/>
-      <c r="M74" s="5" t="s">
-        <v>280</v>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
+        </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53878,8 +53878,10 @@
       <c r="A75" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>283</v>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
+        </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
@@ -58705,8 +58707,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="5"/>
-      <c r="M75" s="5" t="s">
-        <v>283</v>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
+        </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -54202,8 +54202,10 @@
       <c r="A81" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>302</v>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가.csv</t>
+        </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
@@ -59021,8 +59023,10 @@
         <v>0</v>
       </c>
       <c r="L81" s="5"/>
-      <c r="M81" s="5" t="s">
-        <v>302</v>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가.csv</t>
+        </is>
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -54253,8 +54253,10 @@
       <c r="A82" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>305</v>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가-2.csv</t>
+        </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
@@ -59075,8 +59077,10 @@
         <v>0</v>
       </c>
       <c r="L82" s="5"/>
-      <c r="M82" s="5" t="s">
-        <v>305</v>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가-2.csv</t>
+        </is>
       </c>
       <c r="N82" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -54410,8 +54410,10 @@
       <c r="A85" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>313</v>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령.csv</t>
+        </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
@@ -59233,8 +59235,10 @@
         <v>0</v>
       </c>
       <c r="L85" s="5"/>
-      <c r="M85" s="5" t="s">
-        <v>313</v>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령.csv</t>
+        </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -54467,8 +54467,10 @@
       <c r="A86" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>317</v>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령-2.csv</t>
+        </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
@@ -59283,8 +59285,10 @@
         <v>0</v>
       </c>
       <c r="L86" s="5"/>
-      <c r="M86" s="5" t="s">
-        <v>317</v>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥 타령-2.csv</t>
+        </is>
       </c>
       <c r="N86" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -53344,8 +53344,10 @@
       <c r="A65" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>251</v>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 (28).csv</t>
+        </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
@@ -58189,8 +58191,10 @@
         <v>0</v>
       </c>
       <c r="L65" s="5"/>
-      <c r="M65" s="5" t="s">
-        <v>251</v>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 (28).csv</t>
+        </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
         <is>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -50478,45 +50478,61 @@
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>44</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2.csv</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대금키</t>
+        </is>
       </c>
       <c r="F7" s="6"/>
-      <c r="G7" s="4" t="s">
-        <v>17</v>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>46</v>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50524,15 +50540,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4" t="s">
         <v>17</v>
@@ -50544,20 +50562,22 @@
         <v>1</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="5"/>
+      <c r="M8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="O8" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50565,17 +50585,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="4" t="s">
         <v>17</v>
@@ -50587,10 +50605,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>0</v>
@@ -50598,11 +50616,9 @@
       <c r="M9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>54</v>
-      </c>
+      <c r="N9" s="5"/>
       <c r="O9" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50610,30 +50626,32 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="6"/>
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>0</v>
@@ -50641,9 +50659,11 @@
       <c r="M10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="5"/>
+      <c r="N10" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="O10" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50651,12 +50671,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="4" t="s">
@@ -50669,22 +50691,20 @@
         <v>1</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="M11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="5"/>
       <c r="O11" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50692,40 +50712,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N12" s="5"/>
+      <c r="M12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="O12" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50733,13 +50753,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -50753,22 +50773,20 @@
         <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="M13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="5"/>
       <c r="O13" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50821,17 +50839,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>77</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="4" t="s">
         <v>17</v>
@@ -50843,20 +50859,22 @@
         <v>1</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="5"/>
+      <c r="M15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>68</v>
+      </c>
       <c r="O15" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50864,16 +50882,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4" t="s">
@@ -50886,7 +50904,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>6</v>
@@ -50899,7 +50917,7 @@
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50907,15 +50925,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4" t="s">
         <v>17</v>
@@ -50927,22 +50947,20 @@
         <v>1</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>84</v>
-      </c>
+      <c r="M17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="5"/>
       <c r="O17" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50950,40 +50968,42 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="6">
-        <v>93</v>
-      </c>
-      <c r="K18" s="6">
-        <v>4</v>
+      <c r="J18" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N18" s="5"/>
+      <c r="M18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="O18" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50991,42 +51011,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="6">
         <v>93</v>
       </c>
-      <c r="K19" s="6" t="n">
-        <v>18</v>
+      <c r="K19" s="6">
+        <v>4</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51034,7 +51052,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>90</v>
@@ -51054,7 +51072,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>18</v>
@@ -51066,10 +51084,10 @@
         <v>28</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51077,111 +51095,103 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="N21" s="5"/>
+      <c r="M21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="O21" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령-1.csv</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령-1</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
+      <c r="B22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/4</t>
-        </is>
+      <c r="G22" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
-        </is>
+      <c r="M22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>104</v>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-1.csv</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -51197,45 +51207,55 @@
         <v>1</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 25%, 박자 근사</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>105</v>
+          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>49</v>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-2.csv</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-2</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
-      <c r="G24" s="4" t="s">
-        <v>17</v>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H24" s="6" t="n">
         <v>8</v>
@@ -51244,13 +51264,13 @@
         <v>1</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -51259,11 +51279,13 @@
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔레트 외 글자 1, 박자 근사</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>108</v>
+          <t xml:space="preserve">비고 18%, 박자 근사, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51271,63 +51293,75 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E25" s="6"/>
       <c r="F25" s="6"/>
-      <c r="G25" s="4" t="s">
-        <v>34</v>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>112</v>
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 25%, 박자 근사</t>
+        </is>
       </c>
       <c r="O25" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>116</v>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야.csv</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
-      <c r="G26" s="4" t="s">
-        <v>34</v>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="H26" s="6" t="n">
         <v>12</v>
@@ -51336,22 +51370,28 @@
         <v>1</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5" t="s">
-        <v>118</v>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51359,42 +51399,46 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N27" s="5"/>
+        <v>1</v>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1, 박자 근사</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51402,64 +51446,58 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">매화 타령</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E28" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="F28" s="6"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/4</t>
-        </is>
+      <c r="G28" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>125</v>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2.csv</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">몽금포 타령</t>
+          <t xml:space="preserve">담바귀 타령-2</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -51481,26 +51519,28 @@
         <v>1</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔레트 외 글자 1</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="s">
-        <v>128</v>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51508,24 +51548,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물레타령</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
+        <v>114</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4</t>
-        </is>
+      <c r="G30" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>12</v>
@@ -51534,26 +51568,22 @@
         <v>1</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 22%</t>
-        </is>
-      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N30" s="5"/>
       <c r="O30" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51561,24 +51591,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밀양 아리랑</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
+        <v>119</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4</t>
-        </is>
+      <c r="G31" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>12</v>
@@ -51587,10 +51611,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>0</v>
@@ -51600,15 +51624,9 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
-        </is>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51616,11 +51634,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연폭포</t>
+          <t xml:space="preserve">매화 타령</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -51642,26 +51660,26 @@
         <v>1</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
+          <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
       <c r="O32" s="5" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51669,52 +51687,52 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연폭포</t>
+          <t xml:space="preserve">몽금포 타령</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">느리게</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="K33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
       <c r="O33" s="5" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51722,16 +51740,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">뱃노래</t>
+          <t xml:space="preserve">물레타령</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E34" s="6"/>
@@ -51748,24 +51766,26 @@
         <v>1</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 22%</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51773,16 +51793,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">베틀가</t>
+          <t xml:space="preserve">밀양 아리랑</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E35" s="6"/>
@@ -51802,7 +51822,7 @@
         <v>48</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>0</v>
@@ -51819,7 +51839,7 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
         </is>
       </c>
     </row>
@@ -51828,36 +51848,36 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">북간도 아리랑</t>
+          <t xml:space="preserve">박연폭포</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>0</v>
@@ -51867,11 +51887,13 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
-        </is>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51879,14 +51901,18 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가</t>
-        </is>
-      </c>
-      <c r="D37" s="5"/>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느리게</t>
+        </is>
+      </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="4" t="inlineStr">
@@ -51901,10 +51927,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>0</v>
@@ -51914,11 +51940,13 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/사발가.png</t>
-        </is>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51926,11 +51954,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사철가</t>
+          <t xml:space="preserve">뱃노래</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -51942,17 +51970,17 @@
       <c r="F38" s="6"/>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>6</v>
@@ -51960,19 +51988,15 @@
       <c r="L38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 15%</t>
-        </is>
-      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N38" s="5"/>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
         </is>
       </c>
     </row>
@@ -51981,11 +52005,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사철가</t>
+          <t xml:space="preserve">베틀가</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -51997,36 +52021,38 @@
       <c r="F39" s="6"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 18%</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>161</v>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+        </is>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52034,67 +52060,55 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상사 천리몽</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D40" s="5"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/4</t>
-        </is>
+      <c r="G40" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 25%, 박자 근사</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>164</v>
-      </c>
+      <c r="M40" s="6"/>
+      <c r="N40" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="O40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상주 모심기</t>
-        </is>
-      </c>
-      <c r="D41" s="5"/>
+          <t xml:space="preserve">북간도 아리랑</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="4" t="inlineStr">
@@ -52109,7 +52123,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>10</v>
@@ -52117,18 +52131,16 @@
       <c r="L41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 21%</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="s">
-        <v>168</v>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
+        </is>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52136,40 +52148,32 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 타령</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">사발가</t>
+        </is>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>0</v>
@@ -52180,49 +52184,49 @@
         </is>
       </c>
       <c r="N42" s="5"/>
-      <c r="O42" s="5" t="s">
-        <v>172</v>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/사발가.png</t>
+        </is>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>173</v>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2.csv</t>
+        </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 타령-2</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2절</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">사발가-2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K43" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>111</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>0</v>
@@ -52232,9 +52236,15 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
-        <v>176</v>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52242,11 +52252,11 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">석별가</t>
+          <t xml:space="preserve">사철가</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -52255,35 +52265,41 @@
         </is>
       </c>
       <c r="E44" s="6"/>
-      <c r="F44" s="4"/>
+      <c r="F44" s="6"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5" t="s">
-        <v>180</v>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 15%</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+        </is>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52291,11 +52307,11 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">선화공주</t>
+          <t xml:space="preserve">사철가</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -52317,24 +52333,26 @@
         <v>1</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/선화공주.png</t>
-        </is>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 18%</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52342,16 +52360,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신 만고강산</t>
+          <t xml:space="preserve">상사 천리몽</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">남도민요</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E46" s="6"/>
@@ -52368,24 +52386,26 @@
         <v>1</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
-        </is>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 25%, 박자 근사</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52393,50 +52413,48 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신 천안 삼거리</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">상주 모심기</t>
+        </is>
+      </c>
+      <c r="D47" s="5"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
-        </is>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 21%</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52444,11 +52462,11 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고산 타령</t>
+          <t xml:space="preserve">새 타령</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -52456,24 +52474,28 @@
           <t xml:space="preserve">굿거리</t>
         </is>
       </c>
-      <c r="E48" s="6"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>0</v>
@@ -52485,7 +52507,7 @@
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52493,19 +52515,23 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쑥대머리</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단가 중모리</t>
-        </is>
-      </c>
-      <c r="E49" s="6"/>
+          <t xml:space="preserve">새 타령-2</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2절</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
@@ -52516,13 +52542,13 @@
         <v>12</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>0</v>
@@ -52534,7 +52560,7 @@
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52542,20 +52568,20 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쑥대머리</t>
+          <t xml:space="preserve">석별가</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
+      <c r="F50" s="4"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3/4</t>
@@ -52568,10 +52594,10 @@
         <v>1</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>0</v>
@@ -52583,7 +52609,7 @@
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52591,14 +52617,18 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑 낭낭</t>
-        </is>
-      </c>
-      <c r="D51" s="5"/>
+          <t xml:space="preserve">선화공주</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="4" t="inlineStr">
@@ -52607,33 +52637,29 @@
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 19%, 박자 근사</t>
-        </is>
-      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N51" s="5"/>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
+          <t xml:space="preserve">민요채보-1/선화공주.png</t>
         </is>
       </c>
     </row>
@@ -52642,16 +52668,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑 목동</t>
+          <t xml:space="preserve">신 만고강산</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자진모리</t>
+          <t xml:space="preserve">남도민요</t>
         </is>
       </c>
       <c r="E52" s="6"/>
@@ -52662,16 +52688,16 @@
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>0</v>
@@ -52681,27 +52707,23 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박자 근사</t>
-        </is>
-      </c>
+      <c r="N52" s="5"/>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
         </is>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">애수의 가을밤</t>
+          <t xml:space="preserve">신 천안 삼거리</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -52709,11 +52731,7 @@
           <t xml:space="preserve">굿거리</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정악key</t>
-        </is>
-      </c>
+      <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="4" t="inlineStr">
         <is>
@@ -52727,27 +52745,23 @@
         <v>1</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%</t>
-        </is>
-      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N53" s="5"/>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
+          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
         </is>
       </c>
     </row>
@@ -52756,40 +52770,36 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">야월삼경</t>
+          <t xml:space="preserve">신고산 타령</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>0</v>
@@ -52801,7 +52811,7 @@
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52809,54 +52819,56 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>214</v>
+        <v>327</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양류가</t>
+          <t xml:space="preserve">신고산 타령-2</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E55" s="6"/>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
       <c r="F55" s="6"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 20%</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/양류가.png</t>
-        </is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52864,23 +52876,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양류가</t>
+          <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대금키</t>
-        </is>
-      </c>
+          <t xml:space="preserve">단가 중모리</t>
+        </is>
+      </c>
+      <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="4" t="inlineStr">
         <is>
@@ -52894,10 +52902,10 @@
         <v>1</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>0</v>
@@ -52907,15 +52915,9 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/양류가.png</t>
-        </is>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52923,23 +52925,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양산도</t>
+          <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="4" t="inlineStr">
         <is>
@@ -52953,10 +52951,10 @@
         <v>1</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>0</v>
@@ -52967,22 +52965,22 @@
         </is>
       </c>
       <c r="N57" s="5"/>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/양산도.png</t>
-        </is>
+      <c r="O57" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>225</v>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑.csv</t>
+        </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">영천 아리랑</t>
+          <t xml:space="preserve">아리랑</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -52994,11 +52992,11 @@
       <c r="F58" s="6"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>1</v>
@@ -53007,23 +53005,25 @@
         <v>48</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M58" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
-        </is>
-      </c>
-      <c r="O58" s="5" t="s">
-        <v>227</v>
+          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
+        </is>
       </c>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53031,18 +53031,14 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">오봉산 타령</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">아리랑 낭낭</t>
+        </is>
+      </c>
+      <c r="D59" s="5"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="4" t="inlineStr">
@@ -53051,33 +53047,33 @@
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M59" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+          <t xml:space="preserve">비고 19%, 박자 근사</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
         </is>
       </c>
     </row>
@@ -53086,32 +53082,36 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">옹이</t>
-        </is>
-      </c>
-      <c r="D60" s="5"/>
+          <t xml:space="preserve">아리랑 목동</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H60" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>0</v>
@@ -53121,21 +53121,27 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5" t="s">
-        <v>234</v>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+        </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">울산 아가씨</t>
+          <t xml:space="preserve">애수의 가을밤</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -53143,31 +53149,31 @@
           <t xml:space="preserve">굿거리</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정악key</t>
         </is>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="7" t="inlineStr">
         <is>
@@ -53176,12 +53182,12 @@
       </c>
       <c r="N61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔레트 외 글자 1</t>
+          <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
         </is>
       </c>
     </row>
@@ -53190,36 +53196,40 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별가</t>
+          <t xml:space="preserve">야월삼경</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">느릿 굿거리</t>
-        </is>
-      </c>
-      <c r="E62" s="6"/>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F62" s="6"/>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I62" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>0</v>
@@ -53231,7 +53241,7 @@
       </c>
       <c r="N62" s="5"/>
       <c r="O62" s="5" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53239,36 +53249,36 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">잦은 뱃노리</t>
+          <t xml:space="preserve">양류가</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">후렴</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>0</v>
@@ -53280,12 +53290,12 @@
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 17%</t>
+          <t xml:space="preserve">비고 20%</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+          <t xml:space="preserve">민요채보-1/양류가.png</t>
         </is>
       </c>
     </row>
@@ -53294,19 +53304,23 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라도 산타령</t>
+          <t xml:space="preserve">양류가</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
-      </c>
-      <c r="E64" s="6"/>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대금키</t>
+        </is>
+      </c>
       <c r="F64" s="6"/>
       <c r="G64" s="4" t="inlineStr">
         <is>
@@ -53320,10 +53334,10 @@
         <v>1</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>0</v>
@@ -53333,10 +53347,14 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N64" s="5"/>
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
         </is>
       </c>
     </row>
@@ -53344,18 +53362,24 @@
       <c r="A65" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이미지 (28).csv</t>
-        </is>
+      <c r="B65" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목없음 (이미지 (28))</t>
-        </is>
-      </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="6"/>
+          <t xml:space="preserve">양산도</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F65" s="6"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
@@ -53369,56 +53393,52 @@
         <v>1</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 53%, 제목 없음</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="s">
-        <v>254</v>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/양산도.png</t>
+        </is>
       </c>
     </row>
     <row r="66" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제주도 타령.csv</t>
-        </is>
+      <c r="B66" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령</t>
+          <t xml:space="preserve">영천 아리랑</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H66" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I66" s="6" t="n">
         <v>1</v>
@@ -53427,64 +53447,60 @@
         <v>48</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M66" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 19%, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
-        </is>
+          <t xml:space="preserve">박자 근사</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제주도 타령-2.csv</t>
-        </is>
+      <c r="B67" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령-2</t>
+          <t xml:space="preserve">오봉산 타령</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>0</v>
@@ -53496,12 +53512,12 @@
       </c>
       <c r="N67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
+          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
         </is>
       </c>
     </row>
@@ -53509,21 +53525,15 @@
       <c r="A68" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령-3.csv</t>
-        </is>
+      <c r="B68" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멜로디버전</t>
-        </is>
-      </c>
+          <t xml:space="preserve">옹이</t>
+        </is>
+      </c>
+      <c r="D68" s="5"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="4" t="inlineStr">
@@ -53538,65 +53548,63 @@
         <v>1</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">팔레트 외 글자 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N68" s="5"/>
       <c r="O68" s="5" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령.csv</t>
-        </is>
+      <c r="B69" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
+          <t xml:space="preserve">옹헤야</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E69" s="6"/>
+          <t xml:space="preserve">자진모리</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#→C</t>
+        </is>
+      </c>
       <c r="F69" s="6"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>0</v>
@@ -53606,49 +53614,57 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령-4.csv</t>
-        </is>
+      <c r="B70" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
-        </is>
-      </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="6"/>
+          <t xml:space="preserve">울산 아가씨</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F70" s="6"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H70" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I70" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
@@ -53657,12 +53673,12 @@
       </c>
       <c r="N70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 19%</t>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
         </is>
       </c>
     </row>
@@ -53672,24 +53688,16 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령-5.csv</t>
+          <t xml:space="preserve">이미지 (28).csv</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">제목없음 (이미지 (28))</t>
+        </is>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="4" t="inlineStr">
         <is>
@@ -53703,7 +53711,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>9</v>
@@ -53713,12 +53721,16 @@
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N71" s="5"/>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 53%, 제목 없음</t>
+        </is>
+      </c>
       <c r="O71" s="5" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53726,16 +53738,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령 1</t>
+          <t xml:space="preserve">이별가</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">느릿 굿거리</t>
         </is>
       </c>
       <c r="E72" s="6"/>
@@ -53752,26 +53764,22 @@
         <v>1</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%, 박자 근사</t>
-        </is>
-      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N72" s="5"/>
       <c r="O72" s="5" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53779,14 +53787,18 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령 2</t>
-        </is>
-      </c>
-      <c r="D73" s="5"/>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후렴</t>
+        </is>
+      </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="4" t="inlineStr">
@@ -53795,16 +53807,16 @@
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>0</v>
@@ -53816,30 +53828,30 @@
       </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 21%</t>
-        </is>
-      </c>
-      <c r="O73" s="5" t="s">
-        <v>279</v>
+          <t xml:space="preserve">비고 17%</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+        </is>
       </c>
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
-        </is>
+      <c r="B74" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리</t>
+          <t xml:space="preserve">전라도 산타령</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E74" s="6"/>
@@ -53856,7 +53868,7 @@
         <v>1</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>6</v>
@@ -53872,7 +53884,7 @@
       <c r="N74" s="5"/>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
         </is>
       </c>
     </row>
@@ -53882,68 +53894,74 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
+          <t xml:space="preserve">제주도 타령.csv</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리</t>
-        </is>
-      </c>
-      <c r="D75" s="5"/>
+          <t xml:space="preserve">제주도 타령</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 58%, 박자 근사</t>
+          <t xml:space="preserve">비고 19%, 한 장에 두 곡</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
         </is>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>285</v>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령-2.csv</t>
+        </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">청춘가</t>
+          <t xml:space="preserve">제주도 타령-2</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E76" s="6"/>
@@ -53960,38 +53978,42 @@
         <v>1</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 18%</t>
-        </is>
-      </c>
-      <c r="O76" s="5" t="s">
-        <v>287</v>
+          <t xml:space="preserve">한 장에 두 곡</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
       </c>
     </row>
     <row r="77" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>288</v>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령.csv</t>
+        </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쾌지나 칭칭</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -54013,27 +54035,23 @@
         <v>1</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 35%</t>
-        </is>
-      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N77" s="5"/>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
         </is>
       </c>
     </row>
@@ -54042,54 +54060,52 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">태평가</t>
+          <t xml:space="preserve">창부타령 1</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/태평가.png</t>
-        </is>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 17%, 박자 근사</t>
+        </is>
+      </c>
+      <c r="O78" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54097,23 +54113,15 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">통영 개타령</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잦은모리</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">F#</t>
-        </is>
-      </c>
+          <t xml:space="preserve">창부타령 2</t>
+        </is>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="4" t="inlineStr">
         <is>
@@ -54121,7 +54129,7 @@
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>1</v>
@@ -54130,74 +54138,78 @@
         <v>63</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N79" s="5"/>
-      <c r="O79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 21%</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>299</v>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-3.csv</t>
+        </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년 노래</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">잦은모리</t>
+          <t xml:space="preserve">멜로디버전</t>
         </is>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+        <v>1</v>
+      </c>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
         </is>
       </c>
       <c r="O80" s="5" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54206,49 +54218,51 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가.csv</t>
+          <t xml:space="preserve">창부타령-4.csv</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D81" s="5"/>
       <c r="E81" s="6"/>
-      <c r="F81" s="4"/>
+      <c r="F81" s="6"/>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5" t="s">
-        <v>304</v>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 19%</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
+        </is>
       </c>
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54257,12 +54271,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가-2.csv</t>
+          <t xml:space="preserve">창부타령-5.csv</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -54288,10 +54302,10 @@
         <v>1</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>0</v>
@@ -54303,19 +54317,21 @@
       </c>
       <c r="N82" s="5"/>
       <c r="O82" s="5" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>307</v>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
+        </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한강수 타령</t>
+          <t xml:space="preserve">천안 삼거리</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -54337,10 +54353,10 @@
         <v>1</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>0</v>
@@ -54351,27 +54367,27 @@
         </is>
       </c>
       <c r="N83" s="5"/>
-      <c r="O83" s="5" t="s">
-        <v>309</v>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+        </is>
       </c>
     </row>
     <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>310</v>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
+        </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">함양 양잠가</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D84" s="5"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="4" t="inlineStr">
@@ -54386,45 +54402,45 @@
         <v>1</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 29%</t>
-        </is>
-      </c>
-      <c r="O84" s="5" t="s">
-        <v>312</v>
+          <t xml:space="preserve">비고 58%, 박자 근사</t>
+        </is>
+      </c>
+      <c r="O84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
+        </is>
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥 타령.csv</t>
-        </is>
+      <c r="B85" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥 타령</t>
+          <t xml:space="preserve">청춘가</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">늦중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E85" s="6"/>
@@ -54441,10 +54457,10 @@
         <v>1</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>0</v>
@@ -54456,30 +54472,30 @@
       </c>
       <c r="N85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 17%</t>
-        </is>
-      </c>
-      <c r="O85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
-        </is>
+          <t xml:space="preserve">비고 18%</t>
+        </is>
+      </c>
+      <c r="O85" s="5" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥 타령-2.csv</t>
-        </is>
+      <c r="B86" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥 타령</t>
-        </is>
-      </c>
-      <c r="D86" s="5"/>
+          <t xml:space="preserve">쾌지나 칭칭</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="4" t="inlineStr">
@@ -54494,22 +54510,28 @@
         <v>1</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
-        </is>
-      </c>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5" t="s">
-        <v>318</v>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고 35%</t>
+        </is>
+      </c>
+      <c r="O86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+        </is>
       </c>
     </row>
     <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54517,19 +54539,23 @@
         <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>319</v>
+        <v>291</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">희망가</t>
+          <t xml:space="preserve">태평가</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
-      </c>
-      <c r="E87" s="6"/>
+          <t xml:space="preserve">세마치</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F87" s="6"/>
       <c r="G87" s="4" t="inlineStr">
         <is>
@@ -54543,10 +54569,10 @@
         <v>1</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>0</v>
@@ -54557,8 +54583,10 @@
         </is>
       </c>
       <c r="N87" s="5"/>
-      <c r="O87" s="5" t="s">
-        <v>321</v>
+      <c r="O87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/태평가.png</t>
+        </is>
       </c>
     </row>
     <row r="88" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54566,16 +54594,28 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="D88" s="5"/>
-      <c r="E88" s="6"/>
+        <v>294</v>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통영 개타령</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F#</t>
+        </is>
+      </c>
       <c r="F88" s="6"/>
-      <c r="G88" s="4" t="s">
-        <v>17</v>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="H88" s="6" t="n">
         <v>16</v>
@@ -54584,42 +54624,44 @@
         <v>1</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="6"/>
-      <c r="N88" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="O88" s="5"/>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
+        </is>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">옹헤야</t>
+          <t xml:space="preserve">풍년 노래</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자진모리</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C#→C</t>
-        </is>
-      </c>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
+      <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="4" t="inlineStr">
         <is>
@@ -54627,16 +54669,16 @@
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>0</v>
@@ -54648,52 +54690,50 @@
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
+          <t xml:space="preserve">박자 근사</t>
         </is>
       </c>
       <c r="O89" s="5" t="s">
-        <v>46</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>327</v>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가.csv</t>
+        </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고산 타령-2</t>
+          <t xml:space="preserve">풍년가</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자진모리</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C</t>
-        </is>
-      </c>
-      <c r="F90" s="6"/>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E90" s="6"/>
+      <c r="F90" s="4"/>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I90" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>0</v>
@@ -54703,13 +54743,9 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
-        </is>
-      </c>
+      <c r="N90" s="5"/>
       <c r="O90" s="5" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54718,12 +54754,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">는실 타령-2.csv</t>
+          <t xml:space="preserve">풍년가-2.csv</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">는실 타령-2</t>
+          <t xml:space="preserve">풍년가</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -54731,61 +54767,57 @@
           <t xml:space="preserve">굿거리</t>
         </is>
       </c>
-      <c r="E91" s="6"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C#</t>
+        </is>
+      </c>
       <c r="F91" s="6"/>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I91" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 18%, 박자 근사, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
-        </is>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아리랑.csv</t>
-        </is>
+      <c r="B92" s="5" t="s">
+        <v>307</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑</t>
+          <t xml:space="preserve">한강수 타령</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세마치</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E92" s="6"/>
@@ -54802,89 +54834,75 @@
         <v>1</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
-        </is>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구 아리랑-2.csv</t>
-        </is>
+      <c r="B93" s="5" t="s">
+        <v>310</v>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">구 아리랑-2</t>
+          <t xml:space="preserve">함양 양잠가</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">늦중모리</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대금키</t>
-        </is>
-      </c>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I93" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/양류가.png</t>
-        </is>
+          <t xml:space="preserve">비고 29%</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54893,54 +54911,54 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가-2.csv</t>
+          <t xml:space="preserve">흥 타령.csv</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가-2</t>
+          <t xml:space="preserve">흥 타령</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">늦중모리</t>
         </is>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="H94" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I94" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상</t>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
       <c r="N94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사, 한 장에 두 곡</t>
+          <t xml:space="preserve">비고 17%</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
         </is>
       </c>
     </row>
@@ -54950,19 +54968,15 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">닐리리야.csv</t>
+          <t xml:space="preserve">흥 타령-2.csv</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">닐리리야</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
+      </c>
+      <c r="D95" s="5"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="4" t="inlineStr">
@@ -54977,47 +54991,39 @@
         <v>1</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L95" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M95" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중</t>
-        </is>
-      </c>
-      <c r="N95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%, 한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
-        </is>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">담바귀 타령-2.csv</t>
-        </is>
+      <c r="B96" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">담바귀 타령-2</t>
+          <t xml:space="preserve">희망가</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E96" s="6"/>
@@ -55034,10 +55040,10 @@
         <v>1</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>0</v>
@@ -55047,15 +55053,9 @@
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 장에 두 곡</t>
-        </is>
-      </c>
-      <c r="O96" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
-        </is>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/sheets/민요/검수/_목록.xlsx
+++ b/sheets/민요/검수/_목록.xlsx
@@ -55344,60 +55344,74 @@
         <v>343</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>17</v>
+    <row r="7" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_구 아리랑-2.tsv</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늦중모리</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>347</v>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구 아리랑-2.csv</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 구 아리랑 &lt;늦 중모리&gt;. 왼쪽 4줄은 양류가 (채보3). 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
+        </is>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>48</v>
+        <v>345</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>17</v>
@@ -55406,40 +55420,40 @@
         <v>16</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>351</v>
+        <v>48</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>17</v>
@@ -55448,81 +55462,83 @@
         <v>16</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>11</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5" t="s">
-        <v>352</v>
+        <v>47</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>351</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5" t="s">
-        <v>56</v>
+        <v>352</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>34</v>
       </c>
@@ -55533,79 +55549,77 @@
         <v>8</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>357</v>
+        <v>56</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>359</v>
+        <v>60</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>17</v>
@@ -55614,26 +55628,26 @@
         <v>16</v>
       </c>
       <c r="G13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J13" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>31</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55678,18 +55692,18 @@
         <v>363</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>17</v>
@@ -55698,37 +55712,37 @@
         <v>16</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>49</v>
@@ -55740,13 +55754,13 @@
         <v>16</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>6</v>
@@ -55756,24 +55770,24 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>17</v>
@@ -55785,115 +55799,115 @@
         <v>6</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" s="6">
-        <v>93</v>
-      </c>
-      <c r="J18" s="6">
         <v>4</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12정간·굵은 선 3칸마다(인쇄 정간 번호 1~12, 줄 번호 오른쪽 1~8). 손채보, 가사는 각 율명 줄 오른쪽 칸. 10-13 전면 재판독(이전 TSV 는 이미지와 다른 내용). 줄5 번호 위 v 표시는 생략.</t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>369</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>49</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="6">
         <v>93</v>
       </c>
-      <c r="J19" s="6" t="n">
-        <v>18</v>
+      <c r="J19" s="6">
+        <v>4</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>373</v>
+        <v>86</v>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12정간·굵은 선 3칸마다(인쇄 정간 번호 1~12, 줄 번호 오른쪽 1~8). 손채보, 가사는 각 율명 줄 오른쪽 칸. 10-13 전면 재판독(이전 TSV 는 이미지와 다른 내용). 줄5 번호 위 v 표시는 생략.</t>
+        </is>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>90</v>
@@ -55908,13 +55922,13 @@
         <v>16</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>18</v>
@@ -55924,122 +55938,116 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3_는실 타령-1.tsv</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령-1</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/4</t>
-        </is>
+    <row r="22" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="5"/>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는실 타령-1.csv</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 재판독. 원본 한 장에 두 곡 — 앞부분 오른쪽 4줄(원본 줄1~4). 줄1 위 "&lt;둥구래 당실, 굿거리&gt; 후렴", 줄2~4 위 "노래". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개(율명 3개를 위→아래로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸.</t>
-        </is>
+      <c r="M22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>377</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>104</v>
+    <row r="23" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_는실 타령-1.tsv</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-1</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -56050,178 +56058,208 @@
         <v>8</v>
       </c>
       <c r="G23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5" t="s">
-        <v>102</v>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-1.csv</t>
+        </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 여백에 세로로 손글씨 "능계가락 신방곡". 16정간 인쇄 양식이지만 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 오른쪽부터 줄1, 줄2. 줄3 이하(왼쪽 열들)는 빈 격자. 하단 양식 번호 "- 196 -"(16정간 용지). 율명 옆 좁은 가사 칸은 비어 있어 가사는 비움. 한 높이에 나란히 쓴 두 율명은 왼쪽→오른쪽 순으로 적음. 古 모양: 女변 있으면 姑, 없으면 南.</t>
+          <t xml:space="preserve">10-13 재판독. 원본 한 장에 두 곡 — 앞부분 오른쪽 4줄(원본 줄1~4). 줄1 위 "&lt;둥구래 당실, 굿거리&gt; 후렴", 줄2~4 위 "노래". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개(율명 3개를 위→아래로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>17</v>
+    <row r="24" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_는실 타령-2.tsv</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-2</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F24" s="6" t="n">
         <v>8</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5" t="s">
-        <v>106</v>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는실 타령-2.csv</t>
+        </is>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양식이 180° 뒤집혀 인쇄됨(쪽 번호·줄 번호가 거꾸로). 손글씨 기준으로 오른쪽부터 1줄. 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 6줄 5~8정간은 "(간주)": 율명 없이 장구 구음(덩 기덕 덩 다라라 쿵 기덕 쿵 따)만 적혀 비고에 기록. 9줄은 8정간 아래 여백까지 이어 씀(南 ⁚ ⁚ △, 비고 참조). 10줄은 왼쪽 여백의 &lt;전주&gt;(곡 앞에 연주)로 칸 구분이 양식과 달라 정간 위치는 추정, 아래 여백에 X로 지운 칸과 연음이 더 있음. 물결선(요성) 생략. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 재판독. 원본 한 장에 두 곡 — 왼쪽 4줄(원본 줄6~9, 사이 줄5는 세로 메모 "는실 타령 (굿거리)"만 있는 빈 줄, 왼쪽 끝 빈 줄 2개 생략). 왼쪽 위 "&lt;는실 타령 굿거리&gt;". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개(율명 3개를 위→아래로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>34</v>
+        <v>104</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/4</t>
+        </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>385</v>
+        <v>102</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오른쪽 여백에 세로로 손글씨 "능계가락 신방곡". 16정간 인쇄 양식이지만 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 오른쪽부터 줄1, 줄2. 줄3 이하(왼쪽 열들)는 빈 격자. 하단 양식 번호 "- 196 -"(16정간 용지). 율명 옆 좁은 가사 칸은 비어 있어 가사는 비움. 한 높이에 나란히 쓴 두 율명은 왼쪽→오른쪽 순으로 적음. 古 모양: 女변 있으면 姑, 없으면 南.</t>
+        </is>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>34</v>
+    <row r="26" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 닐리리야 (닐리리야).tsv</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3/4</t>
+        </is>
       </c>
       <c r="F26" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K26" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="5"/>
-      <c r="M26" s="5" t="s">
-        <v>114</v>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닐리리야.csv</t>
+        </is>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사가 원본과 달랐음). 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 세마치 3/4. 오른쪽부터 7줄(왼쪽 빈 줄). 율명 오른쪽 ^ 꾸밈은 ^ 로 적음, 潢 옆 작은 ○ 는 생략. 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 왼쪽 줄6~8(검수 내용은 xlsx 가 기준).</t>
         </is>
       </c>
     </row>
     <row r="27" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>10</v>
@@ -56230,84 +56268,80 @@
         <v>10</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 한 줄씩 어긋나고 율명도 원본과 달랐음). 손격자, 12정간·굵은 선 3칸마다 → 세마치 3/4. 10줄, 오른쪽부터 줄1. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 화살표, 두 줄은 가사 없음(줄1 = 줄3 가락). 율명 옆 ^ 꾸밈은 ^ 로 적음.</t>
+          <t xml:space="preserve">양식이 180° 뒤집혀 인쇄됨(쪽 번호·줄 번호가 거꾸로). 손글씨 기준으로 오른쪽부터 1줄. 번호 2개에 걸친 큰 칸 8개에 율명 3개씩(는실 타령과 같은 양식) → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 10-13 8정간으로 다시 만듦. 6줄 5~8정간은 "(간주)": 율명 없이 장구 구음(덩 기덕 덩 다라라 쿵 기덕 쿵 따)만 적혀 비고에 기록. 9줄은 8정간 아래 여백까지 이어 씀(南 ⁚ ⁚ △, 비고 참조). 10줄은 왼쪽 여백의 &lt;전주&gt;(곡 앞에 연주)로 칸 구분이 양식과 달라 정간 위치는 추정, 아래 여백에 X로 지운 칸과 연음이 더 있음. 물결선(요성) 생략. AI 재판독 초안.</t>
         </is>
       </c>
     </row>
     <row r="28" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">매화 타령</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/4</t>
-        </is>
+        <v>384</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F28" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>10</v>
-      </c>
       <c r="H28" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0</v>
+        <v>27</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 "&lt; 매화 타령 굿거리 &gt;". 16정간 양식이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개(가운데 굵은 선), 칸마다 율명 3개(굿거리 3소박, 줄5 정간4만 4개) → 큰 칸 하나 = 정간 하나, 4/4·8. 오른쪽부터 줄1, 율명 7줄에 내용(줄7은 정간1~4만), 줄8~10은 빈 인쇄 줄. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 네모와 화살표, 줄2 위 "전주" 화살표, 줄2 정간1 아래 "&lt;전주&gt;", 줄3 위 "&lt;1절&gt;", 줄4 위 "&lt;2절&gt;", 줄5 정간6 아래 "3절" 네모. 줄6 정간7~8에 X표(삭제 표시).</t>
-        </is>
+        <v>109</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>385</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>392</v>
+    <row r="29" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 (담바귀 타령-2).tsv</t>
+        </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">몽금포 타령</t>
+          <t xml:space="preserve">담바귀 타령-2</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -56324,144 +56358,130 @@
         <v>12</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5" t="s">
-        <v>125</v>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담바귀 타령-2.csv</t>
+        </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "몽금포 타령  굿거리 (서도소리)". 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 선 3칸마다 → 3/4·12. 격자 오른쪽 끝 2줄은 비어 있고(맨 오른쪽 위 여백에 "※ 요성 격하게" 메모) 그 왼쪽부터 율명 6줄 → 줄1="장산곳" 줄. 가사는 각 율명 줄 오른쪽 칸. 한 장 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 왼쪽 줄5~8.</t>
         </is>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물레타령</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4</t>
-        </is>
+        <v>386</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K30" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다) → 중모리 3/4·12. 인쇄 줄번호 1·8은 빈 줄이라 제외, 인쇄 2~7 = 줄1~6. 위쪽 묶음: 후렴=인쇄3·2(줄2·1), 1절=5·4(줄4·3), 2절=7·6(줄6·5). 오른쪽 여백 "남도민요 물레타령 중모리". 율명 오른쪽 겹꺾쇠 꾸밈은 ^ 로 적음(하단 범례 ※潢^→潢無 는 본문 밖이라 생략). 괄호 친 (無)는 無 로 적고 비고. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사가 원본과 달랐음). 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 세마치 3/4. 오른쪽부터 7줄(왼쪽 빈 줄). 율명 오른쪽 ^ 꾸밈은 ^ 로 적음, 潢 옆 작은 ○ 는 생략. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_밀양 아리랑.tsv</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밀양 아리랑</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3/4</t>
-        </is>
+    <row r="31" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>12</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 밀양 아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 오른쪽 4줄은 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 한 줄씩 어긋나고 율명도 원본과 달랐음). 손격자, 12정간·굵은 선 3칸마다 → 세마치 3/4. 10줄, 오른쪽부터 줄1. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 화살표, 두 줄은 가사 없음(줄1 = 줄3 가락). 율명 옆 ^ 꾸밈은 ^ 로 적음.</t>
         </is>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연폭포</t>
+          <t xml:space="preserve">매화 타령</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -56478,99 +56498,95 @@
         <v>8</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "서도민요 박연폭포 '굿거리, 전주'". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 오른쪽 4줄만 내용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 줄1·3, 줄2·4 가락이 거의 같음. 無 뒤 작은 점은 글자 획으로 보고 생략. 줄2 정간5 율명·가사 먹 번짐.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 "&lt; 매화 타령 굿거리 &gt;". 16정간 양식이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개(가운데 굵은 선), 칸마다 율명 3개(굿거리 3소박, 줄5 정간4만 4개) → 큰 칸 하나 = 정간 하나, 4/4·8. 오른쪽부터 줄1, 율명 7줄에 내용(줄7은 정간1~4만), 줄8~10은 빈 인쇄 줄. 가사는 각 율명 줄 오른쪽 칸. 줄1·2 위에 "후렴" 네모와 화살표, 줄2 위 "전주" 화살표, 줄2 정간1 아래 "&lt;전주&gt;", 줄3 위 "&lt;1절&gt;", 줄4 위 "&lt;2절&gt;", 줄5 정간6 아래 "3절" 네모. 줄6 정간7~8에 X표(삭제 표시).</t>
         </is>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연폭포</t>
+          <t xml:space="preserve">몽금포 타령</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">느리게</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="J33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "박연폭포 "체라" (느리게)" 아래 "정악" 표시. 한 곡. 한 줄에 큰 칸 8개(인쇄 정간 2개씩 합친 칸, 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸. 오른쪽 4줄만 사용, 왼쪽 열은 빈 양식. 칸 끝 작은 세모는 △(쉼). 줄4 정간4·5 경계 왼쪽에 &lt; 표시.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "몽금포 타령  굿거리 (서도소리)". 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 선 3칸마다 → 3/4·12. 격자 오른쪽 끝 2줄은 비어 있고(맨 오른쪽 위 여백에 "※ 요성 격하게" 메모) 그 왼쪽부터 율명 6줄 → 줄1="장산곳" 줄. 가사는 각 율명 줄 오른쪽 칸. 한 장 한 곡.</t>
         </is>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_뱃노래.tsv</t>
-        </is>
+    <row r="34" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">뱃노래</t>
+          <t xml:space="preserve">물레타령</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -56582,49 +56598,49 @@
         <v>12</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다) → 중모리 3/4·12. 인쇄 줄번호 1·8은 빈 줄이라 제외, 인쇄 2~7 = 줄1~6. 위쪽 묶음: 후렴=인쇄3·2(줄2·1), 1절=5·4(줄4·3), 2절=7·6(줄6·5). 오른쪽 여백 "남도민요 물레타령 중모리". 율명 오른쪽 겹꺾쇠 꾸밈은 ^ 로 적음(하단 범례 ※潢^→潢無 는 본문 밖이라 생략). 괄호 친 (無)는 無 로 적고 비고. 한 곡.</t>
         </is>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1_베틀가.tsv</t>
+          <t xml:space="preserve">2_밀양 아리랑.tsv</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">베틀가</t>
+          <t xml:space="preserve">밀양 아리랑</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -56645,92 +56661,88 @@
         <v>48</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 밀양 아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 오른쪽 4줄은 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
         </is>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_북간도 아리랑.tsv</t>
-        </is>
+    <row r="36" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>398</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">북간도 아리랑</t>
+          <t xml:space="preserve">박연폭포</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 줄 번호 1~8(오른쪽부터), 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "북간도 아리랑 중모리", 상단 "정악/산조". 줄 위 표기: 줄1~2 후렴, 줄3~4 1절, 줄5~6 2절, 줄7~8 후렴(한 곡). 율명 옆·아래 사선 꾸밈은 ／, 南 옆 작은 꺾쇠는 ^. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "서도민요 박연폭포 '굿거리, 전주'". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 오른쪽 4줄만 내용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 줄1·3, 줄2·4 가락이 거의 같음. 無 뒤 작은 점은 글자 획으로 보고 생략. 줄2 정간5 율명·가사 먹 번짐.</t>
         </is>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/사발가.png</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_사발가.tsv</t>
-        </is>
+    <row r="37" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가</t>
-        </is>
-      </c>
-      <c r="D37" s="5"/>
+          <t xml:space="preserve">박연폭포</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">느리게</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4/4</t>
@@ -56746,38 +56758,38 @@
         <v>4</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목줄 "박연폭포 "체라" (느리게)" 아래 "정악" 표시. 한 곡. 한 줄에 큰 칸 8개(인쇄 정간 2개씩 합친 칸, 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 | 로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸. 오른쪽 4줄만 사용, 왼쪽 열은 빈 양식. 칸 끝 작은 세모는 △(쉼). 줄4 정간4·5 경계 왼쪽에 &lt; 표시.</t>
         </is>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+          <t xml:space="preserve">민요채보-2/뱃노래.png</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1_사철가-경기민요.tsv</t>
+          <t xml:space="preserve">2_뱃노래.tsv</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사철가</t>
+          <t xml:space="preserve">뱃노래</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -56787,20 +56799,20 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>6</v>
@@ -56810,24 +56822,28 @@
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "뱃노래 (굿거리)". 손으로 그린 12정간 격자(굵은 선 3칸마다) → 3/4·12. 오른쪽부터 7줄(맨 왼쪽 2줄은 빈 줄이라 제외). 줄1~2 후렴(에야누야누야/어기여어차), 줄3~7 사설. 南은 古처럼 흘려 씀. 氵仲 은 㳞. 줄1~2 無 옆 작은 꺾쇠는 ^. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>412</v>
+    <row r="39" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_베틀가.tsv</t>
+        </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사철가</t>
+          <t xml:space="preserve">베틀가</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -56837,107 +56853,115 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="J39" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(줄 번호 8→1, 정간 번호 1~16, 하단 "- 196 -")이지만 가로선이 번호 2개(1·2, 3·4 …)마다만 있고 큰 칸 8개에 율명이 2~4개씩 쌓여 있어 큰 칸 하나 = 정간 하나, 4/4·8로 적음(율명은 칸 안 위→아래, 나란히 쓴 두 글자는 붙임). 내용은 오른쪽 1~5줄, 6~8줄 빈 줄. 오른쪽 여백 세로 "경기민요 사철가 굿거리". 줄1~2 위 괄호로 "후렴"(?) 표시, 줄3 위 "전주" 표시 — 줄1~2(지화자/종네 … 종을씨구우나)가 후렴, 줄3~5가 본 노래로 보임(한 곡). 율명 아래 작은 점 두 개(위는 짧은 획처럼 보이기도 함)는 ⁚ 로 통일. 가사 "종"은 "좋"일 수 있음(글자 모양은 종).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>414</v>
+    <row r="40" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/북간도 아리랑.png</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_북간도 아리랑.tsv</t>
+        </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상사 천리몽</t>
+          <t xml:space="preserve">북간도 아리랑</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="H40" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식 위에 손으로 큰 칸을 그림: 인쇄 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 인쇄 줄 2~5번(오른쪽 4줄)에 내용, 인쇄 1번·6~8번 줄은 빔. 가사는 각 율명 줄 바로 오른쪽 칸. 南 흘림이 古처럼 보이는 곳은 南으로 적음. 줄2 정간3·정간7 / 줄3 정간3 가사 칸에 '후' 옆 곡선(괄호·화살표) 표시 있음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 줄 번호 1~8(오른쪽부터), 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "북간도 아리랑 중모리", 상단 "정악/산조". 줄 위 표기: 줄1~2 후렴, 줄3~4 1절, 줄5~6 2절, 줄7~8 후렴(한 곡). 율명 옆·아래 사선 꾸밈은 ／, 南 옆 작은 꺾쇠는 ^. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>416</v>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/사발가.png</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_사발가.tsv</t>
+        </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">상주 모심기</t>
+          <t xml:space="preserve">사발가</t>
         </is>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>4</v>
@@ -56946,34 +56970,38 @@
         <v>4</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 3/4. 내용은 오른쪽 4줄, 왼쪽 빈 줄은 뺌. 1줄 가사 칸 오른쪽 바깥에 "(상주 모심기)"(4~6정간), "(중모리)"(7~9정간) 표기(율명 아님). 여러 칸의 긴 물결선(요성)은 생략. 검은 사각형은 정정 종이를 붙여 다시 쓴 칸으로, 흰 획 글자를 판독. 1·3줄 7~12정간, 2·4줄은 같은 가락.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="42" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>418</v>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_사발가-2.tsv</t>
+        </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 타령</t>
+          <t xml:space="preserve">사발가-2</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -56983,97 +57011,103 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="5"/>
-      <c r="M42" s="5" t="s">
-        <v>169</v>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사발가-2.csv</t>
+        </is>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 가로선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 한 곡. 상단에 "새타령(굿거리) 1", "C#key⟷6판 c key / 정악 청" 메모. 율명 옆 작은 ^ 꾸밈은 ^ 로 적음. 潢 아래 無를 쓴 칸(潢|無)의 요성 곡선·10줄 11정간의 ○ 묶음은 생략. 12정간 끝의 D·○ 모양 표시는 쉼 △ 로 적음. 氵 보이는 女古는 㴌, 氵 없는 것은 姑로 구분. 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 사발가 굿거리. 왼쪽 4줄은 오봉산 타령. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>420</v>
+    <row r="43" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/사철가-경기민요.jpg</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_사철가-경기민요.tsv</t>
+        </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">새 타령-2</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2절</t>
+          <t xml:space="preserve">사철가</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="5" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다) → 3/4·12. 상단 "&lt;2절&gt; 새타령(2) C#키⟷C키". 오른쪽부터 11줄(11줄은 왼쪽 테두리 밖 여백에 율명, 테두리 안 좁은 칸에 가사). 한 곡. 4줄 3~11정간 세로 연음선, 5줄 10~11정간 세로 물결선만 있어 비움. 潢|無 칸의 요성 물결선 생략. 潕 옆 C·&lt; 모양 꾸밈과 㴌·南 옆 ^ 꾸밈은 ^ 로 적음. 4줄 2정간 淋 아래 작은 물결 표시 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식(번호 1~16)이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명이 2~3개씩 쌓인 굿거리 → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 1은 비어 있어 인쇄 열 2를 줄1로, 인쇄 열 2~6 = 줄1~5, 인쇄 열 7·8은 비어 제외. 위쪽 인쇄 열 2~4에 '후렴' 표시와 괄호선(줄1~3 = 후렴 '지화자 좋네…'). 우측 여백 '경기민요 "사철가" "굿거리"'. 가사는 각 율명 줄 오른쪽 칸. 하단 196 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">석별가</t>
+          <t xml:space="preserve">사철가</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -57083,20 +57117,20 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>7</v>
@@ -57106,28 +57140,24 @@
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 원본과 달랐음). 인쇄 12정간 양식, 굵은 선 3칸마다 → 3/4. 오른쪽부터 6줄(7·8줄 빔). 가사는 각 율명 줄 오른쪽 칸. 정간12 의 ―와 ▷ 모양은 ―|△ 로 적음. 율명 오른쪽 ^ 꾸밈은 ^ 로 적음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(줄 번호 8→1, 정간 번호 1~16, 하단 "- 196 -")이지만 가로선이 번호 2개(1·2, 3·4 …)마다만 있고 큰 칸 8개에 율명이 2~4개씩 쌓여 있어 큰 칸 하나 = 정간 하나, 4/4·8로 적음(율명은 칸 안 위→아래, 나란히 쓴 두 글자는 붙임). 내용은 오른쪽 1~5줄, 6~8줄 빈 줄. 오른쪽 여백 세로 "경기민요 사철가 굿거리". 줄1~2 위 괄호로 "후렴"(?) 표시, 줄3 위 "전주" 표시 — 줄1~2(지화자/종네 … 종을씨구우나)가 후렴, 줄3~5가 본 노래로 보임(한 곡). 율명 아래 작은 점 두 개(위는 짧은 획처럼 보이기도 함)는 ⁚ 로 통일. 가사 "종"은 "좋"일 수 있음(글자 모양은 종).</t>
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/선화공주.png</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_선화공주.tsv</t>
-        </is>
+    <row r="45" customFormat="false" ht="165.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">선화공주</t>
+          <t xml:space="preserve">상사 천리몽</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -57144,98 +57174,86 @@
         <v>8</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식 위에 손으로 큰 칸을 그림: 인쇄 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 인쇄 줄 2~5번(오른쪽 4줄)에 내용, 인쇄 1번·6~8번 줄은 빔. 가사는 각 율명 줄 바로 오른쪽 칸. 南 흘림이 古처럼 보이는 곳은 南으로 적음. 줄2 정간3·정간7 / 줄3 정간3 가사 칸에 '후' 옆 곡선(괄호·화살표) 표시 있음.</t>
         </is>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_신 만고강산.tsv</t>
-        </is>
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>416</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신 만고강산</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">남도민요</t>
-        </is>
-      </c>
+          <t xml:space="preserve">상주 모심기</t>
+        </is>
+      </c>
+      <c r="D46" s="5"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="N46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡. 10-15 潢/㴌 재대조.</t>
+        <v>165</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간, 굵은 선 3칸마다 → 3/4. 내용은 오른쪽 4줄, 왼쪽 빈 줄은 뺌. 1줄 가사 칸 오른쪽 바깥에 "(상주 모심기)"(4~6정간), "(중모리)"(7~9정간) 표기(율명 아님). 여러 칸의 긴 물결선(요성)은 생략. 검은 사각형은 정정 종이를 붙여 다시 쓴 칸으로, 흰 획 글자를 판독. 1·3줄 7~12정간, 2·4줄은 같은 가락.</t>
         </is>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_신 천안 삼거리.tsv</t>
-        </is>
+    <row r="47" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>418</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신 천안 삼거리</t>
+          <t xml:space="preserve">새 타령</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -57245,102 +57263,102 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간, 굵은 가로선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 한 곡. 상단에 "새타령(굿거리) 1", "C#key⟷6판 c key / 정악 청" 메모. 율명 옆 작은 ^ 꾸밈은 ^ 로 적음. 潢 아래 無를 쓴 칸(潢|無)의 요성 곡선·10줄 11정간의 ○ 묶음은 생략. 12정간 끝의 D·○ 모양 표시는 쉼 △ 로 적음. 氵 보이는 女古는 㴌, 氵 없는 것은 姑로 구분. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">신고산 타령</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">새 타령-2</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2절</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="N48" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(번호 1~16)에 번호 2개씩 걸친 큰 칸 8개, 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 8정간 4/4(굿거리). 오른쪽 여백 제목 "신고산 타령"/부제 "굿거리", 줄1·2 위 "후렴" 묶음. 내용 있는 줄은 오른쪽 1~5줄(6~8줄 빈 줄 제외), 줄5는 정간4까지(정간3~4에 긴 사선). 가사는 각 율명 줄 오른쪽 칸. 율명 오른쪽 작은 ^ 꾸밈은 ^ 로 적음.</t>
+        <v>173</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다) → 3/4·12. 상단 "&lt;2절&gt; 새타령(2) C#키⟷C키". 오른쪽부터 11줄(11줄은 왼쪽 테두리 밖 여백에 율명, 테두리 안 좁은 칸에 가사). 한 곡. 4줄 3~11정간 세로 연음선, 5줄 10~11정간 세로 물결선만 있어 비움. 潢|無 칸의 요성 물결선 생략. 潕 옆 C·&lt; 모양 꾸밈과 㴌·南 옆 ^ 꾸밈은 ^ 로 적음. 4줄 2정간 淋 아래 작은 물결 표시 생략.</t>
         </is>
       </c>
     </row>
     <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쑥대머리</t>
+          <t xml:space="preserve">석별가</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">단가 중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -57352,54 +57370,58 @@
         <v>12</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="N49" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~8 줄, 1~12 정간), 12정간·굵은 선 3칸마다 → 3/4·12, 8줄 모두 사용, 한 곡. 오른쪽 여백 '1. (쑥대머리) 단가, 중모리'. 이전 판독의 淋·淋潢 은 대부분 氵姑(㴌). 潢 오른쪽 아래 겹 곡선 ')' 꾸밈은 潢^ 로 적음 — 하단 메모칸 '※ 潢) ⇒ 潢 아래 無(곡선)' 즉 潢에서 無로 꺾어 내리는 표시. 가사는 각 율명 줄 오른쪽 칸.</t>
+        <v>177</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 판독은 율명·가사 위치가 원본과 달랐음). 인쇄 12정간 양식, 굵은 선 3칸마다 → 3/4. 오른쪽부터 6줄(7·8줄 빔). 가사는 각 율명 줄 오른쪽 칸. 정간12 의 ―와 ▷ 모양은 ―|△ 로 적음. 율명 오른쪽 ^ 꾸밈은 ^ 로 적음.</t>
         </is>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>434</v>
+    <row r="50" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/선화공주.png</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_선화공주.tsv</t>
+        </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쑥대머리</t>
+          <t xml:space="preserve">선화공주</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>5</v>
@@ -57408,93 +57430,97 @@
         <v>5</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="N50" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다), 5줄 사용(6~8줄 빈칸). 오른쪽 여백 "&lt;ス&gt;" 쑥대머리 중모리. 潢 뒤 이중 곡선 꼬리는 ^ 로 표기 — 하단 메모 "※ 潢(꼬리) ⇒ 潢→無"(꼬리 = 無로 흘러내림 표시). (無)는 괄호 친 無. "- 197 -"는 양식 용지 번호.</t>
+        <v>181</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독(이전 16정간·6줄 판독은 구조가 틀렸음). 16정간 양식(번호 1~16)이지만 굵은 선이 2칸마다이고 칸 안 가로선이 없어 큰 칸 8개, 칸마다 율명 2~4개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 줄 1 은 비어 인쇄 2~6줄을 줄1~5로, 7·8줄 비어 #줄수 5. 우측 여백 "(정악?)" "선화공주" "굿거리". 끝의 쉼표는 D·▷처럼 흘려 쓴 것도 △. 하단 "196" 무시. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="51" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
+          <t xml:space="preserve">민요채보-2/신 만고강산.png</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_아리랑 낭낭.tsv</t>
+          <t xml:space="preserve">2_신 만고강산.tsv</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑 낭낭</t>
-        </is>
-      </c>
-      <c r="D51" s="5"/>
+          <t xml:space="preserve">신 만고강산</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남도민요</t>
+        </is>
+      </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움). 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+          <t xml:space="preserve">민요채보-1/신 천안 삼거리.png</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_아리랑 목동.tsv</t>
+          <t xml:space="preserve">1_신 천안 삼거리.tsv</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑 목동</t>
+          <t xml:space="preserve">신 천안 삼거리</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">자진모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -57503,47 +57529,43 @@
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|―율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="53" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_애수의 가을밤.tsv</t>
-        </is>
+      <c r="A53" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>430</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">애수의 가을밤</t>
+          <t xml:space="preserve">신고산 타령</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -57560,45 +57582,45 @@
         <v>8</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(번호 1~16)에 번호 2개씩 걸친 큰 칸 8개, 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 8정간 4/4(굿거리). 오른쪽 여백 제목 "신고산 타령"/부제 "굿거리", 줄1·2 위 "후렴" 묶음. 내용 있는 줄은 오른쪽 1~5줄(6~8줄 빈 줄 제외), 줄5는 정간4까지(정간3~4에 긴 사선). 가사는 각 율명 줄 오른쪽 칸. 율명 오른쪽 작은 ^ 꾸밈은 ^ 로 적음.</t>
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">야월삼경</t>
+          <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">단가 중모리</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -57616,43 +57638,39 @@
         <v>8</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 오른쪽 상단 "야월삼경 &lt;중모리&gt; C#키". 12정간, 굵은 선 3칸마다 → 3/4. 오른쪽 맨 끝 빈 칸 제외, 오른쪽부터 8줄 사용(왼쪽 2칸 빈 줄). 가사는 각 율명 줄 오른쪽 칸. 정간 안 짧은 가로선·작은 사선 점은 모두 ― 로 적음. 줄3·줄5 등 청성(㴌·㳞·湳) 가락 반복. 한 곡.</t>
+        <v>194</v>
+      </c>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~8 줄, 1~12 정간), 12정간·굵은 선 3칸마다 → 3/4·12, 8줄 모두 사용, 한 곡. 오른쪽 여백 '1. (쑥대머리) 단가, 중모리'. 이전 판독의 淋·淋潢 은 대부분 氵姑(㴌). 潢 오른쪽 아래 겹 곡선 ')' 꾸밈은 潢^ 로 적음 — 하단 메모칸 '※ 潢) ⇒ 潢 아래 無(곡선)' 즉 潢에서 無로 꺾어 내리는 표시. 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/양류가.png</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_양류가.tsv</t>
-        </is>
+    <row r="55" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>434</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양류가</t>
+          <t xml:space="preserve">쑥대머리</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -57664,49 +57682,49 @@
         <v>12</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다), 5줄 사용(6~8줄 빈칸). 오른쪽 여백 "&lt;ス&gt;" 쑥대머리 중모리. 潢 뒤 이중 곡선 꼬리는 ^ 로 표기 — 하단 메모 "※ 潢(꼬리) ⇒ 潢→無"(꼬리 = 無로 흘러내림 표시). (無)는 괄호 친 無. "- 197 -"는 양식 용지 번호.</t>
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/양류가.png</t>
+          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_양류가.tsv</t>
+          <t xml:space="preserve">2_아리랑.tsv</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양류가</t>
+          <t xml:space="preserve">아리랑</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -57724,93 +57742,95 @@
         <v>4</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="5"/>
-      <c r="M56" s="5" t="s">
-        <v>218</v>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑.csv</t>
+        </is>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 양류가(굿거리). 오른쪽 4줄은 구 아리랑-2. 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 본조 아리랑(제목 열 "아리랑(세마치)"). 왼쪽 4줄은 밀양 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/양산도.png</t>
+          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_양산도.tsv</t>
+          <t xml:space="preserve">2_아리랑 낭낭.tsv</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">양산도</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
-      </c>
+          <t xml:space="preserve">아리랑 낭낭</t>
+        </is>
+      </c>
+      <c r="D57" s="5"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 ―·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네.. 10-15 潢/㴌 재대조.</t>
+        <v>200</v>
+      </c>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움). 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>450</v>
+    <row r="58" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/아리랑 목동.png</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_아리랑 목동.tsv</t>
+        </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">영천 아리랑</t>
+          <t xml:space="preserve">아리랑 목동</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세마치</t>
+          <t xml:space="preserve">자진모리</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -57819,47 +57839,47 @@
         </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K58" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="N58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자: 한 줄에 큰 칸 8개(칸 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4(근사, 원본 표기는 세마치). 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사 칸의 &lt; 표시(쓰라·영·아리랑·고·날·산·큰 앞)는 바로 위 정간 끝에 ‹ 로 적음. 南 옆 작은 꺾쇠는 ^.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|―율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+          <t xml:space="preserve">민요채보-1/애수의 가을밤.png</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_오봉산 타령.tsv</t>
+          <t xml:space="preserve">1_애수의 가을밤.tsv</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">오봉산 타령</t>
+          <t xml:space="preserve">애수의 가을밤</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -57876,43 +57896,47 @@
         <v>8</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 오봉산 타령 굿거리. 오른쪽 4줄은 사발가-2. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
+        <v>207</v>
+      </c>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식 용지(- 196 -)에 번호 2개(1·2, 3·4…)씩 묶은 큰 칸 8개, 칸마다 율명 3단 쌓임(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 열 2~7을 줄1~6으로(인쇄 열 1·8 빈 줄). 가사는 각 율명 열 오른쪽 칸. 㳞·南 뒤 ㄱ/3 모양 꾸밈은 ^ 로. 無 위 작은 ˘ 표시(대부분의 無)는 생략. 줄3·줄6 5~8정간 같은 가락. 오른쪽 여백 key 지우고 정악key. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">옹이</t>
-        </is>
-      </c>
-      <c r="D60" s="5"/>
+          <t xml:space="preserve">야월삼경</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3/4</t>
@@ -57922,44 +57946,44 @@
         <v>12</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="N60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(번호 없음), 12정간 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 줄1은 전주(가사 없음, 위에 '전주' 글씨). 줄2~9는 8정간까지만 쓰고 끝에 ―|△, 줄10만 12정간까지. 칸 안 짧은 가로선은 ―로 적음. 머리 '옹이', '조창건', 오른쪽 위 채보 메모, 줄10 왼쪽 여백·위에 작은 메모 있음(생략).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 오른쪽 상단 "야월삼경 &lt;중모리&gt; C#키". 12정간, 굵은 선 3칸마다 → 3/4. 오른쪽 맨 끝 빈 칸 제외, 오른쪽부터 8줄 사용(왼쪽 2칸 빈 줄). 가사는 각 율명 줄 오른쪽 칸. 정간 안 짧은 가로선·작은 사선 점은 모두 ― 로 적음. 줄3·줄5 등 청성(㴌·㳞·湳) 가락 반복. 한 곡.</t>
         </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+          <t xml:space="preserve">민요채보-1/양류가.png</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_울산 아가씨.tsv</t>
+          <t xml:space="preserve">1_양류가.tsv</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">울산 아가씨</t>
+          <t xml:space="preserve">양류가</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -57976,54 +58000,58 @@
         <v>12</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|―?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽 여백 "양류가 「바른 굿거리」". 오른쪽 4줄 사용(5~8줄 빈칸). 이전 판독의 姑 다수가 실제로는 南(十+冂 흘림)이라 바로잡음; 女+古 모양만 姑. 無 위 작은 ˇ 는 無 첫 획으로 봄. 2·4줄 가락 동일, 1·3줄 끝부분 유사. 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>458</v>
+    <row r="62" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/양류가.png</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_양류가.tsv</t>
+        </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별가</t>
+          <t xml:space="preserve">양류가</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">느릿 굿거리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>4</v>
@@ -58032,7 +58060,7 @@
         <v>4</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J62" s="6" t="n">
         <v>3</v>
@@ -58042,187 +58070,185 @@
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="N62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(196)이지만 번호 2개(1·2,3·4…)씩 큰 칸 8개로 쓰고 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개, 4/4·8(는실 타령 양식). 맨 오른쪽 인쇄 열(1)은 비어 열2를 줄1로, 열2~5 = 줄1~4, 열6~8 빈 줄 제외. 오른쪽 여백에 "이별가", "느릿 굿거리", "노래따라". 율명 오른쪽 작은 3자·s자 꾸밈(汰·潢·南 등)과 칸 사이 세로 물결선·닫는 곡선 요성 표시는 기호표에 없어 생략, 꺾쇠 모양만 ^. 가사 칸의 늘임 ㅣ 는 생략. 멜리스마 모음(아·이)이 가사로 붙음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 양류가(굿거리). 오른쪽 4줄은 구 아리랑-2. 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
         </is>
       </c>
     </row>
     <row r="63" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
+          <t xml:space="preserve">민요채보-2/양산도.png</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_잦은 뱃노리.tsv</t>
+          <t xml:space="preserve">2_양산도.tsv</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">잦은 뱃노리</t>
+          <t xml:space="preserve">양산도</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">후렴</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡. 10-15 潢/㴌 재대조.</t>
+        <v>222</v>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(기울어짐), 굵은 가로선 3칸마다 → 12정간 세마치 3/4. 오른쪽 끝 1열·왼쪽 2열은 빈 줄이라 제외, 내용 6줄. 줄1 후반 ―·△·／(사선) 다수. 가사는 각 율명 줄 오른쪽 칸(줄2-6 가사 칸의 · 점, 줄5-11·12 가사 옆 ✓ 표시는 생략). 가사: 에허이여 / 양덕 맹산 흐르는 물 / 감돌아 든다고 부벽루 / 하로다 에헤라 놓아라 / 아니 못놓겠네 능지를 / 하여도 못놓겠네.. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_전라도 산타령.tsv</t>
-        </is>
+    <row r="64" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">전라도 산타령</t>
+          <t xml:space="preserve">영천 아리랑</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="N64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자: 한 줄에 큰 칸 8개(칸 가운데 점선), 칸마다 율명 2~4개 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4(근사, 원본 표기는 세마치). 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사 칸의 &lt; 표시(쓰라·영·아리랑·고·날·산·큰 앞)는 바로 위 정간 끝에 ‹ 로 적음. 南 옆 작은 꺾쇠는 ^.</t>
         </is>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
+    <row r="65" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_오봉산 타령.tsv</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오봉산 타령</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="5"/>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이미지 (28).csv</t>
-        </is>
+      <c r="M65" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="N65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 제목 없는 손채보, 손으로 그린 격자(번호 없음), 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽 끝 열은 비어 있어 그 왼쪽 율명 열을 줄1로 셈. 내용은 2줄뿐(나머지 왼쪽 줄은 빈 칸). 줄2는 율명 없이 세로·사선 획과 세모만 있음(장구 등 반주 표시로 보임) — 기호표에 없어 모두 ﾉ 로 적고 비고에 모양. 가사: 깐다 깐다 정든 님이 떠나간다.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 왼쪽 4줄(원본 줄5~8) = 오봉산 타령 굿거리. 오른쪽 4줄은 사발가-2. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
         </is>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_제주도 타령 닐리리야 (제주도 타령).tsv</t>
-        </is>
+    <row r="66" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>454</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중모리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">옹이</t>
+        </is>
+      </c>
+      <c r="D66" s="5"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3/4</t>
@@ -58232,51 +58258,49 @@
         <v>12</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제주도 타령.csv</t>
-        </is>
+      <c r="M66" s="5" t="s">
+        <v>231</v>
       </c>
       <c r="N66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 오른쪽 줄1~4(검수 내용은 xlsx 가 기준).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(번호 없음), 12정간 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 줄1은 전주(가사 없음, 위에 '전주' 글씨). 줄2~9는 8정간까지만 쓰고 끝에 ―|△, 줄10만 12정간까지. 칸 안 짧은 가로선은 ―로 적음. 머리 '옹이', '조창건', 오른쪽 위 채보 메모, 줄10 왼쪽 여백·위에 작은 메모 있음(생략).</t>
         </is>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_제주도 타령 (제주도 타령-2).tsv</t>
+          <t xml:space="preserve">3_울산 아가씨.tsv</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제주도 타령-2</t>
+          <t xml:space="preserve">울산 아가씨</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -58288,49 +58312,39 @@
         <v>12</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="J67" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K67" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제주도 타령-2.csv</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 오른쪽 줄1~4.</t>
+      <c r="M67" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|―?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">멜로디버전</t>
-        </is>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3/4</t>
@@ -58340,155 +58354,155 @@
         <v>12</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령-3.csv</t>
+          <t xml:space="preserve">이미지 (28).csv</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12, 10줄. 각 율명 열 오른쪽 가사 칸은 모두 비어 있음(멜로디만). 짝수 줄(2·4·8·10)은 거의 같은 南/無南/無潢/仲姑 가락 반복, 3·7줄 동일. 5·6줄 가운데 잉크 번짐. 이전 판독의 姑/僙 대부분은 南/姑의 오독이라 정정.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 없는 손채보, 손으로 그린 격자(번호 없음), 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽 끝 열은 비어 있어 그 왼쪽 율명 열을 줄1로 셈. 내용은 2줄뿐(나머지 왼쪽 줄은 빈 칸). 줄2는 율명 없이 세로·사선 획과 세모만 있음(장구 등 반주 표시로 보임) — 기호표에 없어 모두 ﾉ 로 적고 비고에 모양. 가사: 깐다 깐다 정든 님이 떠나간다.</t>
         </is>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_창부 타령-2.tsv</t>
-        </is>
+    <row r="69" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>458</v>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
+          <t xml:space="preserve">이별가</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">느릿 굿거리</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G69" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K69" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령.csv</t>
-        </is>
+      <c r="M69" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="N69" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 ― 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(196)이지만 번호 2개(1·2,3·4…)씩 큰 칸 8개로 쓰고 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개, 4/4·8(는실 타령 양식). 맨 오른쪽 인쇄 열(1)은 비어 열2를 줄1로, 열2~5 = 줄1~4, 열6~8 빈 줄 제외. 오른쪽 여백에 "이별가", "느릿 굿거리", "노래따라". 율명 오른쪽 작은 3자·s자 꾸밈(汰·潢·南 등)과 칸 사이 세로 물결선·닫는 곡선 요성 표시는 기호표에 없어 생략, 꺾쇠 모양만 ^. 가사 칸의 늘임 ㅣ 는 생략. 멜리스마 모음(아·이)이 가사로 붙음.</t>
         </is>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="73.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
+          <t xml:space="preserve">민요채보-3/잦은 뱃노리.png</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1_창부 타령-3.tsv</t>
+          <t xml:space="preserve">3_잦은 뱃노리.tsv</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
-        </is>
-      </c>
-      <c r="D70" s="5"/>
+          <t xml:space="preserve">잦은 뱃노리</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">후렴</t>
+        </is>
+      </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령-4.csv</t>
-        </is>
-      </c>
-      <c r="N70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만. 10-15 潢/㴌 재대조.</t>
+      <c r="M70" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 선 4칸마다) → 4/4·16. 오른쪽 끝 빈 줄 1개 제외하고 9줄. 머리 "잦은 뱃노래 &lt;자즌몰이&gt; 후렴", "3번". 古 모양 글자는 南 흘림으로 봄(仲·南·無 진행). 줄3 12정간 아래 굵은 덧줄, 줄2·6 일부 동그라미 묶음(생략). 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>476</v>
+    <row r="71" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/전라도 산타령.png</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_전라도 산타령.tsv</t>
+        </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령</t>
+          <t xml:space="preserve">전라도 산타령</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -58500,142 +58514,156 @@
         <v>12</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부타령-5.csv</t>
-        </is>
+      <c r="M71" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="N71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 제목 "창부타령 1 굿거리", 오른쪽 위 "C#키"·"1절". 오른쪽부터 10줄, 가사는 각 율명 줄 오른쪽 좁은 칸. 흘림 南(十+冂)·姑(女古)를 구별, 氵仲(神 모양)=㳞, 氵姑=㴌, 氵南=湳. 한 칸에 위아래로 쌓인 두 글자는 |로 구분. 줄1은 시작 '아아니'와 각 장 끝 '이' 받침 가락. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(197), 위에 열 번호 1~8, 왼쪽 정간 번호 1~12, 굵은 선 3칸마다 → 3/4·12. 인쇄 열 1은 비어 있어 열 2~5를 줄1~4로 셈(열 6~8 빈 줄). 오른쪽 여백에 제목 '전라도 산타령 중모리'. 黃·潢 오른쪽의 겹 곡선 )) 요성 표시는 ^ 로 적음(아래 범례: 潢)) ⇒ 潢 다음 無로 흘림). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>478</v>
+    <row r="72" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 닐리리야 (제주도 타령).tsv</t>
+        </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령 1</t>
+          <t xml:space="preserve">제주도 타령</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="5"/>
-      <c r="M72" s="5" t="s">
-        <v>273</v>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령.csv</t>
+        </is>
       </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 196)이나 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 2~4개씩 세로로 적힘 → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 8줄 모두 사용, 가사는 각 율명 열 바로 오른쪽 칸. 한 곡: 줄1 '아니 아니 노지는 못하리라' 후렴, 줄2~7 1절(우연히 길을 갈 적에…, 줄7 후반 후렴 반복), 줄8 위 '?절'(2절?) 표기 후 '백구야 날지 마라…'. 古처럼 흘린 글자 중 다리가 있는 것은 南, 女변이 있는 것은 姑. 神처럼 쓴 氵仲은 㳞, 氵 하나로 이어 쓴 '神姑'는 㳞㴌으로 적음. 가사 칸의 ㅣ(늘임)·&lt; 표시는 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 오른쪽 줄1~4(검수 내용은 xlsx 가 기준).</t>
         </is>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>480</v>
+    <row r="73" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_제주도 타령 (제주도 타령-2).tsv</t>
+        </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">창부타령 2</t>
-        </is>
-      </c>
-      <c r="D73" s="5"/>
+          <t xml:space="preserve">제주도 타령-2</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중모리</t>
+        </is>
+      </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K73" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="5"/>
-      <c r="M73" s="5" t="s">
-        <v>277</v>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제주도 타령-2.csv</t>
+        </is>
       </c>
       <c r="N73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 번호 196)이지만 번호 2개(1·2, 3·4 …)마다 굵은 선으로 묶인 큰 칸 8개에 율명이 3~4개씩 쌓인 양식 → 큰 칸 하나 = 정간 하나, 4/4·8. 율명은 칸 안 위→아래로 | 로 이어 씀. 오른쪽부터 8줄 모두 사용, 한 곡. 상단 줄5·6 위에 '3절 | 2절끝' 메모. 가사는 각 율명 줄 오른쪽 칸. 1줄 8정간(15·16)은 큰 X 지움표로 비어 있음. 女변 古형은 姑, 十+冂형은 南(氵 붙으면 湳). 같은 높이 나란히 쓴 두 음(㳞㴌, 無南, 仲姑 등)은 붙여 씀.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 오른쪽 줄1~4.</t>
         </is>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+          <t xml:space="preserve">민요채보-1/창부 타령-2.jpg</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_천안 삼거리.tsv</t>
+          <t xml:space="preserve">1_창부 타령-2.tsv</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -58652,16 +58680,16 @@
         <v>12</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K74" s="6" t="n">
         <v>0</v>
@@ -58669,32 +58697,32 @@
       <c r="L74" s="5"/>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
+          <t xml:space="preserve">창부타령.csv</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12행, 오른쪽부터 10줄. 한 곡. 제목 '창부타령 乙 굿거리', 왼쪽 위 '2절'. 가사는 각 율명 줄 오른쪽 칸(줄6은 가사 없음). 女 없는 十+冂 모양은 南, 女+古는 姑, 氵+같은 모양은 㴌 으로 적음(南/姑·㴌/湳 구별이 가장 불확실). 潢 은 정자(氵黃)와 약자(氵廿+갈고리) 두 모양 모두 潢. 율명 칸의 작은 빗금·짧은 선은 연음 ― 로 적음. 줄 끝 쉼은 작은 세모(▷ 모양) △. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1_천안 삼거리.tsv</t>
-        </is>
+    <row r="75" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>478</v>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안 삼거리</t>
-        </is>
-      </c>
-      <c r="D75" s="5"/>
+          <t xml:space="preserve">창부타령 1</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">굿거리</t>
+        </is>
+      </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4/4</t>
@@ -58704,56 +58732,50 @@
         <v>8</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="5"/>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
-        </is>
+      <c r="M75" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="N75" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 196)이나 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 2~4개씩 세로로 적힘 → 큰 칸 하나 = 정간 하나, 4/4·8(근사). 8줄 모두 사용, 가사는 각 율명 열 바로 오른쪽 칸. 한 곡: 줄1 '아니 아니 노지는 못하리라' 후렴, 줄2~7 1절(우연히 길을 갈 적에…, 줄7 후반 후렴 반복), 줄8 위 '?절'(2절?) 표기 후 '백구야 날지 마라…'. 古처럼 흘린 글자 중 다리가 있는 것은 南, 女변이 있는 것은 姑. 神처럼 쓴 氵仲은 㳞, 氵 하나로 이어 쓴 '神姑'는 㳞㴌으로 적음. 가사 칸의 ㅣ(늘임)·&lt; 표시는 생략.</t>
         </is>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">청춘가</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">창부타령 2</t>
+        </is>
+      </c>
+      <c r="D76" s="5"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>8</v>
@@ -58762,43 +58784,39 @@
         <v>8</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K76" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="N76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 오른쪽 여백에 세로로 "청춘가 굿거리". 가사는 각 율명 줄 오른쪽 칸. 1절(줄1~4) 이팔은 청춘에 소년 몸 되어서 문명의 학문을 닦아 봅시다, 2절(줄5~8) 청춘 홍안을 (네) 자랑 마라 덧없는 세월에 백발이 되누나 — 같은 가락 두 번(줄1~4 ≒ 줄5~8, 청성 위주로 약간 다름). 줄4 정간1~3 가사 칸은 지운 흔적. 南 오른쪽 작은 꺾쇠는 ^.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 양식(용지 번호 196)이지만 번호 2개(1·2, 3·4 …)마다 굵은 선으로 묶인 큰 칸 8개에 율명이 3~4개씩 쌓인 양식 → 큰 칸 하나 = 정간 하나, 4/4·8. 율명은 칸 안 위→아래로 | 로 이어 씀. 오른쪽부터 8줄 모두 사용, 한 곡. 상단 줄5·6 위에 '3절 | 2절끝' 메모. 가사는 각 율명 줄 오른쪽 칸. 1줄 8정간(15·16)은 큰 X 지움표로 비어 있음. 女변 古형은 姑, 十+冂형은 南(氵 붙으면 湳). 같은 높이 나란히 쓴 두 음(㳞㴌, 無南, 仲姑 등)은 붙여 씀.</t>
         </is>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3_쾌지나 칭칭.tsv</t>
-        </is>
+    <row r="77" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>470</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쾌지나 칭칭</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">멜로디버전</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -58810,224 +58828,228 @@
         <v>12</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5"/>
-      <c r="M77" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="N77" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-3.csv</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 인쇄 번호 없음. 12정간·굵은 선 3칸마다 → 3/4·12, 10줄. 각 율명 열 오른쪽 가사 칸은 모두 비어 있음(멜로디만). 짝수 줄(2·4·8·10)은 거의 같은 南/無南/無潢/仲姑 가락 반복, 3·7줄 동일. 5·6줄 가운데 잉크 번짐. 이전 판독의 姑/僙 대부분은 南/姑의 오독이라 정정.</t>
         </is>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="73.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-2/태평가.png</t>
+          <t xml:space="preserve">민요채보-1/창부 타령-3.jpg</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_태평가.tsv</t>
+          <t xml:space="preserve">1_창부 타령-3.tsv</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">태평가</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세마치</t>
-        </is>
-      </c>
+          <t xml:space="preserve">창부타령</t>
+        </is>
+      </c>
+      <c r="D78" s="5"/>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K78" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="5"/>
-      <c r="M78" s="5" t="s">
-        <v>291</v>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-4.csv</t>
+        </is>
       </c>
       <c r="N78" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3_통영 개타령.tsv</t>
-        </is>
+    <row r="79" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>476</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">통영 개타령</t>
+          <t xml:space="preserve">창부타령</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">잦은모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F79" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="J79" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="K79" s="9" t="n">
+      <c r="K79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="5"/>
-      <c r="M79" s="5" t="s">
-        <v>294</v>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">창부타령-5.csv</t>
+        </is>
       </c>
       <c r="N79" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無―仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡. 10-15 潢/㴌 재대조.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 제목 "창부타령 1 굿거리", 오른쪽 위 "C#키"·"1절". 오른쪽부터 10줄, 가사는 각 율명 줄 오른쪽 좁은 칸. 흘림 南(十+冂)·姑(女古)를 구별, 氵仲(神 모양)=㳞, 氵姑=㴌, 氵南=湳. 한 칸에 위아래로 쌓인 두 글자는 |로 구분. 줄1은 시작 '아아니'와 각 장 끝 '이' 받침 가락. 한 곡.</t>
         </is>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>494</v>
+    <row r="80" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_천안 삼거리.tsv</t>
+        </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년 노래</t>
+          <t xml:space="preserve">천안 삼거리</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">잦은모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K80" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="5"/>
-      <c r="M80" s="5" t="s">
-        <v>299</v>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천안 삼거리-굿거리.csv</t>
+        </is>
       </c>
       <c r="N80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 큰 칸 양식: 한 줄에 큰 칸 8개(굵은 가로선 2칸마다, 칸 안 점선으로 3소박), 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 율명 위→아래 | 로 4/4·8(근사). 율명 10줄(오른쪽 4줄 + 가운데 겹선 + 왼쪽 6줄), 오른쪽=1. 가사는 각 율명 줄 오른쪽 칸. 머리 "자즌모리 &lt;그정을 1박으로&gt;", 왼쪽 위 "간주는 6박". 줄1·5 일부는 가사 없는 반주성 줄. 하단 "+4" 용지 번호 무시. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>496</v>
+    <row r="81" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/천안 삼거리.png</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1_천안 삼거리.tsv</t>
+        </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">천안 삼거리</t>
+        </is>
+      </c>
+      <c r="D81" s="5"/>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F81" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K81" s="6" t="n">
         <v>0</v>
@@ -59035,25 +59057,25 @@
       <c r="L81" s="5"/>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가.csv</t>
+          <t xml:space="preserve">천안 삼거리-굿거리-2.csv</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 번호 1~8, 정간 번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 왼쪽 빈 줄 1개 제외. 가사는 각 율명 줄 오른쪽 칸. 줄3·줄7 6정간 아래 경계에 &lt; 표시(‹). 줄2·줄6 12정간 아래 글자는 亻黃(僙)로 판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16번호 양식이지만 번호 2개(1·2, 3·4 …)에 걸친 큰 칸 8개에 율명 3개씩(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 4/4·8(근사). 인쇄 1열은 비어 있어 인쇄 2·3·4열을 줄1~3으로 함(5~8열 빈칸). 오른쪽 여백에 "천안삼거리 굿거리". 가사는 각 율명 줄 오른쪽 칸. 한 큰 칸에 가사가 위·아래로 나뉜 곳(흥…응)은 붙여 씀. 하단 "- 196 -"은 양식 번호. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="82" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">풍년가</t>
+          <t xml:space="preserve">청춘가</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -59079,33 +59101,35 @@
         <v>96</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="5"/>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍년가-2.csv</t>
-        </is>
+      <c r="M82" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="N82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 제목 '풍년가 (굿거리)', 오른쪽 위 C#key. 인쇄 양식 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽부터 8줄 사용(왼쪽 2줄 빈 줄 제외). 줄1~4 1절(풍년이 왔네…금수강산으로), 줄5~8 2절(얼씨구나 좋다…화전놀이를 가세)로 같은 가락 반복. 연음 짧은 가로/사선 획은 ―, 아주 작은 점은 ·. 줄4 정간11 체크(✓)는 ^ 로 적음. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 오른쪽 여백에 세로로 "청춘가 굿거리". 가사는 각 율명 줄 오른쪽 칸. 1절(줄1~4) 이팔은 청춘에 소년 몸 되어서 문명의 학문을 닦아 봅시다, 2절(줄5~8) 청춘 홍안을 (네) 자랑 마라 덧없는 세월에 백발이 되누나 — 같은 가락 두 번(줄1~4 ≒ 줄5~8, 청성 위주로 약간 다름). 줄4 정간1~3 가사 칸은 지운 흔적. 南 오른쪽 작은 꺾쇠는 ^.</t>
         </is>
       </c>
     </row>
     <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>500</v>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/쾌지나 칭칭.png</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3_쾌지나 칭칭.tsv</t>
+        </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한강수 타령</t>
+          <t xml:space="preserve">쾌지나 칭칭</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -59122,162 +59146,168 @@
         <v>12</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K83" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="N83" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식 12정간(굵은 선 3칸마다, 줄 번호 1~8), 8줄 모두 사용. 오른쪽 여백에 세로로 "한강수 타령 굿거리" 표기. 줄5~8은 후렴(에헤 에헤요 얼삼마 둥개디어라 내사랑아). 가사는 각 율명 줄 오른쪽 칸. 하단 "- 197 -"은 양식 용지 번호.</t>
+        <v>288</v>
+      </c>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "쾌지나 칭칭 굿거리 2절 1절 후렴 &lt;정악청?&gt;". 손으로 그린 격자, 한 줄 12정간(굵은 선 3칸마다) → 3/4·12. 내용은 오른쪽 3줄뿐(그 왼쪽·오른쪽 끝 빈 줄 제외): 줄1=후렴, 줄2=1절, 줄3=2절(머리 표기 순서). 가사는 각 율명 줄 오른쪽 칸. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>502</v>
+    <row r="84" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/태평가.png</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2_태평가.tsv</t>
+        </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">함양 양잠가</t>
+          <t xml:space="preserve">태평가</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">세마치</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F84" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K84" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="N84" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 양식은 16정간이나 손으로 번호 2개(1·2…)마다 굵은 선을 그어 큰 칸 8개, 칸마다 율명 2~4개(굿거리) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 1열은 비어 있어 인쇄 2열=줄1, 3열=줄2, 4열=줄3, 5열=줄4; 6~8열 빈 줄. 상단 "3후렴→2", "노래 5→4". 줄2는 정간5부터 비어 있음. 하단 메모 "※潢) → 僙에서 無까지 회성" — 潢無) 등 ) 표시는 회성. 오른쪽 여백 제목 "함양 양잠가 굿거리". 古 모양(十+冂)=南, 女+古=姑, 氵+姑=㴌로 구별.</t>
+        <v>291</v>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 상단 제목 "태평가 &lt;세마치&gt; C# key". 손으로 그린 12정간 격자, 굵은 가로선 3칸마다 → 3/4·12. 맨 오른쪽 줄은 비어 있어 제외, 오른쪽부터 9줄. 가사는 각 율명 줄 오른쪽 칸. 5~8줄(후렴)은 氵 청성. 6줄 7~12정간 가사(니나/노/오오)는 6줄 칸에 있음(5줄 7~12정간은 가사 없음). 율명 위 호선·곡선 꾸밈과 가사 칸 ㅣ 늘임 표시는 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
+          <t xml:space="preserve">민요채보-3/통영 개타령.png</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1_흥 타령.tsv</t>
+          <t xml:space="preserve">3_통영 개타령.tsv</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥 타령</t>
+          <t xml:space="preserve">통영 개타령</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">늦중모리</t>
+          <t xml:space="preserve">잦은모리</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="5"/>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥 타령.csv</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'. 10-15 潢/㴌 재대조.</t>
+      <c r="M85" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 한 줄 16정간(굵은 가로선 4칸마다) → 4/4·16. 머리 "통영 개타령 &lt;잦은모리&gt; (F# key)". 맨 오른쪽 1줄(潢/無―仲/南/南, 가사 개야개)은 크게 X로 지운 초안이라 제외, 그 왼쪽 빈 칸 다음 줄부터 줄1. 왼쪽 빈 줄 제외 4줄. 가사는 각 율명 줄 바로 오른쪽 칸. 가사 칸의 쉼표·ㅣ 표시는 생략. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
     <row r="86" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥 타령</t>
-        </is>
-      </c>
-      <c r="D86" s="5"/>
+          <t xml:space="preserve">풍년 노래</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잦은모리</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I86" s="6" t="n">
         <v>80</v>
@@ -59285,36 +59315,34 @@
       <c r="J86" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="K86" s="9" t="n">
+      <c r="K86" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="5"/>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥 타령-2.csv</t>
-        </is>
+      <c r="M86" s="5" t="s">
+        <v>299</v>
       </c>
       <c r="N86" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(위 줄 번호 1~8, 왼쪽 정간 번호 1~12), 12정간·굵은 선 3칸마다 → 3/4·12. 내용은 오른쪽 7줄(줄8 빈 줄 제외). 오른쪽 여백에 "2절", "흥타령" 표기 — 한 곡. 가사는 각 율명 줄 오른쪽 좁은 칸. 율명 오른쪽 곡선 꾸밈( )) 모양)은 ^ 로 적음. 하단 "- 197 -"은 양식 번호.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 큰 칸 양식: 한 줄에 큰 칸 8개(굵은 가로선 2칸마다, 칸 안 점선으로 3소박), 칸마다 율명 1~4개 → 큰 칸 1개 = 정간 1개, 율명 위→아래 | 로 4/4·8(근사). 율명 10줄(오른쪽 4줄 + 가운데 겹선 + 왼쪽 6줄), 오른쪽=1. 가사는 각 율명 줄 오른쪽 칸. 머리 "자즌모리 &lt;그정을 1박으로&gt;", 왼쪽 위 "간주는 6박". 줄1·5 일부는 가사 없는 반주성 줄. 하단 "+4" 용지 번호 무시. 한 곡.</t>
         </is>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">희망가</t>
+          <t xml:space="preserve">풍년가</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -59332,38 +59360,36 @@
         <v>8</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K87" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="5"/>
-      <c r="M87" s="5" t="s">
-        <v>319</v>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍년가.csv</t>
+        </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다, 하단 - 197 -) → 3/4·12, 오른쪽부터 8줄(제목 옆 '중모리'). 가사는 각 율명 줄 오른쪽 칸. 侑 모양은 㑲(亻南)로 적음. 無·㒇 위 작은 v/∪ 꾸밈은 ^ 로. 짧은 사선 획은 ―, 둥근 점은 · 로 구분. 가사 칸의 점 표시는 생략. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 번호 1~8, 정간 번호 1~12, 굵은 선 3칸마다) → 3/4·12. 오른쪽부터 8줄 모두 사용, 왼쪽 빈 줄 1개 제외. 가사는 각 율명 줄 오른쪽 칸. 줄3·줄7 6정간 아래 경계에 &lt; 표시(‹). 줄2·줄6 12정간 아래 글자는 亻黃(僙)로 판독.</t>
         </is>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/는실 타령.png</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3_는실 타령-2.tsv</t>
-        </is>
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>498</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">는실 타령-2</t>
+          <t xml:space="preserve">풍년가</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -59373,23 +59399,23 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F88" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G88" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G88" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="H88" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K88" s="6" t="n">
         <v>0</v>
@@ -59397,34 +59423,30 @@
       <c r="L88" s="5"/>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">는실 타령-2.csv</t>
+          <t xml:space="preserve">풍년가-2.csv</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 재판독. 원본 한 장에 두 곡 — 왼쪽 4줄(원본 줄6~9, 사이 줄5는 세로 메모 "는실 타령 (굿거리)"만 있는 빈 줄, 왼쪽 끝 빈 줄 2개 생략). 왼쪽 위 "&lt;는실 타령 굿거리&gt;". 손으로 그린 격자: 한 줄에 큰 칸 8개(굵은 선 2칸마다), 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개(율명 3개를 위→아래로), 8정간 4/4(근사). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 제목 '풍년가 (굿거리)', 오른쪽 위 C#key. 인쇄 양식 12정간·굵은 선 3칸마다 → 3/4·12. 오른쪽부터 8줄 사용(왼쪽 2줄 빈 줄 제외). 줄1~4 1절(풍년이 왔네…금수강산으로), 줄5~8 2절(얼씨구나 좋다…화전놀이를 가세)로 같은 가락 반복. 연음 짧은 가로/사선 획은 ―, 아주 작은 점은 ·. 줄4 정간11 체크(✓)는 ^ 로 적음. 한 곡.</t>
         </is>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/밀양 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_아리랑.tsv</t>
-        </is>
+    <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>500</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리랑</t>
+          <t xml:space="preserve">한강수 타령</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">세마치</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -59436,60 +59458,54 @@
         <v>12</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K89" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="5"/>
-      <c r="M89" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아리랑.csv</t>
-        </is>
+      <c r="M89" s="5" t="s">
+        <v>307</v>
       </c>
       <c r="N89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 본조 아리랑(제목 열 "아리랑(세마치)"). 왼쪽 4줄은 밀양 아리랑. 한 장에 두 곡: 오른쪽 4줄(줄1~4)=본조 아리랑(맨 오른쪽 제목 열 "아리랑(세마치)", 율명 아님), 왼쪽 4줄(줄5~8)=밀양아리랑(가운데 제목 열 "(밀양아리랑) 세마치"). 손으로 그린 12정간, 굵은 선 3칸마다 → 3/4. 맨 오른쪽 제목 열 위 주석 "※ 潢 ⇓ 潢ㅏ"(潢 옆 ㅏ 꾸밈 설명) → 줄3 정간5 潢^ 로 적음. 南을 十+口(古 모양)로 흘려 쓴 곳 많음 → 南. 無潢無 왼쪽 { 묶음은 비고. 가사는 각 율명 줄 오른쪽 칸, ㅣ(늘임)는 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식 12정간(굵은 선 3칸마다, 줄 번호 1~8), 8줄 모두 사용. 오른쪽 여백에 세로로 "한강수 타령 굿거리" 표기. 줄5~8은 후렴(에헤 에헤요 얼삼마 둥개디어라 내사랑아). 가사는 각 율명 줄 오른쪽 칸. 하단 "- 197 -"은 양식 용지 번호.</t>
         </is>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/양류가.png</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3_구 아리랑-2.tsv</t>
-        </is>
+    <row r="90" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>502</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">구 아리랑-2</t>
+          <t xml:space="preserve">함양 양잠가</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">늦중모리</t>
+          <t xml:space="preserve">굿거리</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3/4</t>
+          <t xml:space="preserve">4/4</t>
         </is>
       </c>
       <c r="F90" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>4</v>
@@ -59498,103 +59514,93 @@
         <v>4</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K90" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="5"/>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구 아리랑-2.csv</t>
-        </is>
-      </c>
-      <c r="N90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 구 아리랑 &lt;늦 중모리&gt;. 왼쪽 4줄은 양류가 (채보3). 한 장에 두 곡: 오른쪽 줄1~4 "구 아리랑 &lt;늦 중모리&gt;(#키)", 빈 열 1개 건너 줄5~8 "양류가(굿거리)(#키)". 12정간, 굵은 선 3칸마다. 맨 왼쪽 빈 열 2개는 줄수에서 뺌. 古처럼 흘려 쓴 글자는 南으로 판독(姑는 女古로 구별됨).</t>
+      <c r="M90" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 양식은 16정간이나 손으로 번호 2개(1·2…)마다 굵은 선을 그어 큰 칸 8개, 칸마다 율명 2~4개(굿거리) → 큰 칸 1개 = 정간 1개, 4/4·8. 인쇄 1열은 비어 있어 인쇄 2열=줄1, 3열=줄2, 4열=줄3, 5열=줄4; 6~8열 빈 줄. 상단 "3후렴→2", "노래 5→4". 줄2는 정간5부터 비어 있음. 하단 메모 "※潢) → 僙에서 無까지 회성" — 潢無) 등 ) 표시는 회성. 오른쪽 여백 제목 "함양 양잠가 굿거리". 古 모양(十+冂)=南, 女+古=姑, 氵+姑=㴌로 구별.</t>
         </is>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">민요채보-3/오봉산 타령.png</t>
+          <t xml:space="preserve">민요채보-1/흥 타령.png</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_사발가-2.tsv</t>
+          <t xml:space="preserve">1_흥 타령.tsv</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가-2</t>
+          <t xml:space="preserve">흥 타령</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">늦중모리</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4</t>
+          <t xml:space="preserve">3/4</t>
         </is>
       </c>
       <c r="F91" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G91" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G91" s="6" t="n">
-        <v>4</v>
-      </c>
       <c r="H91" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K91" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">사발가-2.csv</t>
-        </is>
-      </c>
-      <c r="N91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10-13 전면 재판독. 한 장에 두 곡 — 오른쪽 4줄(원본 줄1~4) = 사발가 굿거리. 왼쪽 4줄은 오봉산 타령. 한 장에 두 곡: 제목 "오봉산 타령 굿거리, 사발가 굿거리". 손으로 그린 격자, 한 줄에 큰 칸 8개(칸마다 율명 3개, 굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4(근사). 맨 오른쪽 빈 열과 두 곡 사이 빈 열은 줄로 세지 않음. 줄1~4 사발가(석탄 백탄…허송 세월을 갈아라, 줄4 아래 4칸 빈칸), 줄5~8 오봉산 타령(오봉산 꼭대기…). 가사는 각 율명 줄 오른쪽 칸.</t>
+          <t xml:space="preserve">흥 타령.csv</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간, 굵은 선 3칸마다 → 늦중모리 3/4. 오른쪽부터 8줄, 한 곡. 1~2줄 머리에 '후렴'(1·2줄 위 화살표). 이전 판독에서 姑로 적었던 흘림 글자 대부분이 南(十+内 모양)임. 하단 범례: 姑 → 떠는음, 南 → 뻗는음(?), 潢 → 꺾는음; 潢 오른쪽 겹친 꺾임 표시(》)는 꺾는음 표기라 생략, 물결선(요성)도 생략하고 일부 비고. 7줄 10~12정간은 X로 지워져 비움. 가사: 흥타령 '꿈이로다 ... 무엇을 하리'. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령 닐리리야.png</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_제주도 타령 닐리리야 (닐리리야).tsv</t>
-        </is>
+    <row r="92" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>506</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">닐리리야</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">굿거리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">흥 타령</t>
+        </is>
+      </c>
+      <c r="D92" s="5"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3/4</t>
@@ -59604,51 +59610,47 @@
         <v>12</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K92" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">닐리리야.csv</t>
+          <t xml:space="preserve">흥 타령-2.csv</t>
         </is>
       </c>
       <c r="N92" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4·12). 한 장에 두 곡: 맨 오른쪽 칸 제목 "제주도 타령 &lt;중모리&gt;"(줄 번호에 넣지 않음), 줄1~4 제주도 타령. 줄5 율명 칸에 부제 "닐리리야 (굿거리)"를 세로로 써서 율명 없음, 줄6~8 닐리리야. 맨 왼쪽 빈 줄은 #줄수에서 뺌. 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 줄 끝의 D 모양 표시는 흘려 쓴 △로 봄. 古처럼 흘린 글자 중 女변 없는 것은 南, 있는 것은 姑. 10-15 潢/㴌 재대조. 10-15 사용자가 xlsx 를 두 곡으로 분리 — 이 TSV 는 원본 왼쪽 줄6~8(검수 내용은 xlsx 가 기준).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(위 줄 번호 1~8, 왼쪽 정간 번호 1~12), 12정간·굵은 선 3칸마다 → 3/4·12. 내용은 오른쪽 7줄(줄8 빈 줄 제외). 오른쪽 여백에 "2절", "흥타령" 표기 — 한 곡. 가사는 각 율명 줄 오른쪽 좁은 칸. 율명 오른쪽 곡선 꾸밈( )) 모양)은 ^ 로 적음. 하단 "- 197 -"은 양식 번호.</t>
         </is>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/제주도 타령.png</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2_제주도 타령 (담바귀 타령-2).tsv</t>
-        </is>
+    <row r="93" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>508</v>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">담바귀 타령-2</t>
+          <t xml:space="preserve">희망가</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">굿거리</t>
+          <t xml:space="preserve">중모리</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -59660,29 +59662,27 @@
         <v>12</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K93" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="5"/>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">담바귀 타령-2.csv</t>
-        </is>
+      <c r="M93" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="N93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄된 12정간 양식(줄 1~8, 정간 1~12, 굵은 선 3칸마다 → 3/4). 한 장에 두 곡: 1~4줄 "제주도 타령 중모리", 5~8줄 "담바귀 타령 굿거리"(오른쪽 여백에도 같은 표기). 아래 여백 "담바귀 ⇒ 담배 남령초 (울산지역에 담배 제작 산지로 유명)". 가사는 각 율명 줄 바로 오른쪽 좁은 칸. 1줄 9·7줄 2·8줄 9 가사 칸의 ㅣ(늘임 표시)는 생략. 女변 있는 흘림은 姑, 없는 것은 南. 10-15 潢/㴌 재대조. 10-15 한 장 두 곡 분리 — 이 TSV 는 원본 왼쪽 줄5~8.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다, 하단 - 197 -) → 3/4·12, 오른쪽부터 8줄(제목 옆 '중모리'). 가사는 각 율명 줄 오른쪽 칸. 侑 모양은 㑲(亻南)로 적음. 無·㒇 위 작은 v/∪ 꾸밈은 ^ 로. 짧은 사선 획은 ―, 둥근 점은 · 로 구분. 가사 칸의 점 표시는 생략. 한 곡.</t>
         </is>
       </c>
     </row>
